--- a/data/equipment.xlsx
+++ b/data/equipment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="593">
   <si>
     <t>Zone</t>
   </si>
@@ -96,1690 +96,1702 @@
     <t>import</t>
   </si>
   <si>
+    <t>2cef56f7-953b-437a-855c-ad7477ce9521</t>
+  </si>
+  <si>
+    <t>RWC 5</t>
+  </si>
+  <si>
+    <t>ROW-3</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>8b692832-d75d-493c-b39e-1578b114f0c0</t>
+  </si>
+  <si>
+    <t>Cotterman Ladder</t>
+  </si>
+  <si>
+    <t>cotterman</t>
+  </si>
+  <si>
+    <t>ROW-4</t>
+  </si>
+  <si>
+    <t>3658ffc9-f89c-48ad-8e79-4dcb7d0b15f2</t>
+  </si>
+  <si>
+    <t>RWC 5 Cage</t>
+  </si>
+  <si>
+    <t>ROW-5</t>
+  </si>
+  <si>
+    <t>a2ee0a3b-5aa7-4c94-94dc-d279bdf063a3</t>
+  </si>
+  <si>
+    <t>RWC 6</t>
+  </si>
+  <si>
+    <t>ROW-6</t>
+  </si>
+  <si>
+    <t>39a04271-6c0d-4865-a676-0906c1526ab1</t>
+  </si>
+  <si>
+    <t>ROW-7</t>
+  </si>
+  <si>
+    <t>a9ee7ff9-3538-4dc8-8945-2683e32b4c30</t>
+  </si>
+  <si>
+    <t>RWC 6 cage</t>
+  </si>
+  <si>
+    <t>ROW-8</t>
+  </si>
+  <si>
+    <t>f782a468-c067-4953-868d-379e2e920b13</t>
+  </si>
+  <si>
+    <t>MP 8</t>
+  </si>
+  <si>
+    <t>ROW-9</t>
+  </si>
+  <si>
+    <t>4db7cf5f-b961-4696-8351-040d6b2f5f69</t>
+  </si>
+  <si>
+    <t>MP 7</t>
+  </si>
+  <si>
+    <t>ROW-10</t>
+  </si>
+  <si>
+    <t>235c7d80-3649-4250-a1e3-4022b98fd89f</t>
+  </si>
+  <si>
+    <t>MP 7 (across from it)</t>
+  </si>
+  <si>
+    <t>ROW-11</t>
+  </si>
+  <si>
+    <t>ce14e5a5-7e71-410c-b2eb-627dd8563211</t>
+  </si>
+  <si>
+    <t>Green Mile (DD 145)</t>
+  </si>
+  <si>
+    <t>ROW-12</t>
+  </si>
+  <si>
+    <t>6e3a3f1f-7c87-48a4-ae77-b3048805d200</t>
+  </si>
+  <si>
+    <t>Inbound</t>
+  </si>
+  <si>
+    <t>Far out past PID1</t>
+  </si>
+  <si>
+    <t>Mezzanine</t>
+  </si>
+  <si>
+    <t>ROW-13</t>
+  </si>
+  <si>
+    <t>0514913d-62b9-4fca-b9f4-82ca605fc24e</t>
+  </si>
+  <si>
+    <t>PID 1</t>
+  </si>
+  <si>
+    <t>ROW-14</t>
+  </si>
+  <si>
+    <t>71a93da5-ad06-41bb-9f1f-de4eb9383d9b</t>
+  </si>
+  <si>
+    <t>PID 2</t>
+  </si>
+  <si>
+    <t>ROW-15</t>
+  </si>
+  <si>
+    <t>db640f79-8e80-4018-ac98-f1a28d7e8aa9</t>
+  </si>
+  <si>
+    <t>PID 3</t>
+  </si>
+  <si>
+    <t>ROW-16</t>
+  </si>
+  <si>
+    <t>8c91c7dd-5e8d-4801-bf19-f428dfcdd83e</t>
+  </si>
+  <si>
+    <t>PID 4</t>
+  </si>
+  <si>
+    <t>ROW-17</t>
+  </si>
+  <si>
+    <t>6cb030d8-46cd-417e-826d-d8322978f21e</t>
+  </si>
+  <si>
+    <t>PID 5</t>
+  </si>
+  <si>
+    <t>ROW-18</t>
+  </si>
+  <si>
+    <t>53379c02-3be1-4b35-bb02-0f44c03529e2</t>
+  </si>
+  <si>
+    <t>PID 6</t>
+  </si>
+  <si>
+    <t>ROW-19</t>
+  </si>
+  <si>
+    <t>427f01d6-482f-4ba7-ba29-5495cdf15ebf</t>
+  </si>
+  <si>
+    <t>DD #211</t>
+  </si>
+  <si>
+    <t>ROW-20</t>
+  </si>
+  <si>
+    <t>48e971b9-0d03-48e0-9338-1e45d25bc944</t>
+  </si>
+  <si>
+    <t>ROW-21</t>
+  </si>
+  <si>
+    <t>b8b34aa4-c5c8-4154-98a0-6a92e3d9c034</t>
+  </si>
+  <si>
+    <t>DD #212/ E3</t>
+  </si>
+  <si>
+    <t>ROW-22</t>
+  </si>
+  <si>
+    <t>9e97d300-5262-4329-b759-f3df8665bc64</t>
+  </si>
+  <si>
+    <t>DD 212, near PID platform</t>
+  </si>
+  <si>
+    <t>ROW-23</t>
+  </si>
+  <si>
+    <t>2bd5a83b-275b-4333-9a52-9101de48aa29</t>
+  </si>
+  <si>
+    <t>PID Injection 4</t>
+  </si>
+  <si>
+    <t>PL 38</t>
+  </si>
+  <si>
+    <t>Fastener coming loose</t>
+  </si>
+  <si>
+    <t>ea866b38-ece8-4679-b3ee-abd455ead407</t>
+  </si>
+  <si>
+    <t>DD #212</t>
+  </si>
+  <si>
+    <t>ROW-25</t>
+  </si>
+  <si>
+    <t>f4c233cd-f4dd-41b5-9f4e-0ae5103e82fe</t>
+  </si>
+  <si>
+    <t>DD #213</t>
+  </si>
+  <si>
+    <t>ROW-26</t>
+  </si>
+  <si>
+    <t>Should this be moved sides</t>
+  </si>
+  <si>
+    <t>94500175-1a63-4cf4-8bb7-4ee33f237b4e</t>
+  </si>
+  <si>
+    <t>ROW-27</t>
+  </si>
+  <si>
+    <t>4ae96ea4-b9c3-412d-afa8-e08fced0203c</t>
+  </si>
+  <si>
+    <t>DD #214</t>
+  </si>
+  <si>
+    <t>ROW-28</t>
+  </si>
+  <si>
+    <t>6b87a16e-53da-41af-882c-462e8f5adbb6</t>
+  </si>
+  <si>
+    <t>PL- PID 5</t>
+  </si>
+  <si>
+    <t>15 step</t>
+  </si>
+  <si>
+    <t>7d3ee982-f3e0-450b-84cb-5dd8e21dc62b</t>
+  </si>
+  <si>
+    <t>ROW-30</t>
+  </si>
+  <si>
+    <t>6a13c193-e559-4b85-86ab-f83d31f04ffc</t>
+  </si>
+  <si>
+    <t>PL Inbound Dock</t>
+  </si>
+  <si>
+    <t>a10c3402-441a-49be-9b24-0ccb195feb67</t>
+  </si>
+  <si>
+    <t>DD #215</t>
+  </si>
+  <si>
+    <t>ROW-32</t>
+  </si>
+  <si>
+    <t>d6acb300-e761-4091-8124-975fada53487</t>
+  </si>
+  <si>
+    <t>Dd #215</t>
+  </si>
+  <si>
+    <t>PL-, PID 5</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Pole on steps</t>
+  </si>
+  <si>
+    <t>5088c370-6880-46bf-9e4c-64db32c15d75</t>
+  </si>
+  <si>
+    <t>ROW-34</t>
+  </si>
+  <si>
+    <t>fbabeda4-950b-43ca-b706-51b506471555</t>
+  </si>
+  <si>
+    <t>ROW-35</t>
+  </si>
+  <si>
+    <t>Needs ID</t>
+  </si>
+  <si>
+    <t>d8b12dba-673f-404a-849e-2e085628be51</t>
+  </si>
+  <si>
+    <t>DD #216</t>
+  </si>
+  <si>
+    <t>ROW-36</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2a05767c-d1c9-404c-a3bd-dd922b53a9eb</t>
+  </si>
+  <si>
+    <t>PL-, PID 3</t>
+  </si>
+  <si>
+    <t>24cf99cf-4c5a-461f-9677-c2816c7678e7</t>
+  </si>
+  <si>
+    <t>DD #217</t>
+  </si>
+  <si>
+    <t>ROW-38</t>
+  </si>
+  <si>
+    <t>90b768fd-60a0-436c-bfab-cd5ea5cb9466</t>
+  </si>
+  <si>
+    <t>DD #218</t>
+  </si>
+  <si>
+    <t>ROW-39</t>
+  </si>
+  <si>
+    <t>8e60390c-39f8-48af-9af0-8486da4fa241</t>
+  </si>
+  <si>
+    <t>ROW-40</t>
+  </si>
+  <si>
+    <t>b1760f21-af78-40de-99ef-72029348fdab</t>
+  </si>
+  <si>
+    <t>PL 20, Line 4</t>
+  </si>
+  <si>
+    <t>slight_bend</t>
+  </si>
+  <si>
+    <t>fbfe537c-0e47-4467-9cfe-4421ecf452e1</t>
+  </si>
+  <si>
+    <t>DD #219</t>
+  </si>
+  <si>
+    <t>ROW-42</t>
+  </si>
+  <si>
+    <t>8778c5e0-ab89-4c23-85f6-cc7a9f656f54</t>
+  </si>
+  <si>
+    <t>DD #220</t>
+  </si>
+  <si>
+    <t>ROW-43</t>
+  </si>
+  <si>
+    <t>ffc6a089-0d95-4fed-8625-787ad5de280e</t>
+  </si>
+  <si>
+    <t>ROW-44</t>
+  </si>
+  <si>
+    <t>6d29357d-f7c0-49ad-8cbc-3a99266e3a09</t>
+  </si>
+  <si>
+    <t>PL 24/IB Dock</t>
+  </si>
+  <si>
+    <t>04e07606-0ae6-4d8a-aaf2-f7efc8a5c6c8</t>
+  </si>
+  <si>
+    <t>DD #221</t>
+  </si>
+  <si>
+    <t>ROW-46</t>
+  </si>
+  <si>
+    <t>5dbf9c15-0510-4bcb-9774-5bfb332189b4</t>
+  </si>
+  <si>
+    <t>DD #221, merge</t>
+  </si>
+  <si>
+    <t>ROW-47</t>
+  </si>
+  <si>
+    <t>299847d0-9c4f-4635-a915-a7f2977afe92</t>
+  </si>
+  <si>
+    <t>PL PID 1</t>
+  </si>
+  <si>
+    <t>1248fe5c-a2f5-4a8c-ab94-b848b329e839</t>
+  </si>
+  <si>
+    <t>DD  221</t>
+  </si>
+  <si>
+    <t>PL 36</t>
+  </si>
+  <si>
+    <t>7 step ladder</t>
+  </si>
+  <si>
+    <t>9d0aa434-d1e3-4def-adb9-7b11297a39ef</t>
+  </si>
+  <si>
+    <t>Line 11</t>
+  </si>
+  <si>
+    <t>ROW-50</t>
+  </si>
+  <si>
+    <t>7ee89b55-2eee-4621-85e3-7e6ed51b583c</t>
+  </si>
+  <si>
+    <t>DD #222</t>
+  </si>
+  <si>
+    <t>ROW-51</t>
+  </si>
+  <si>
+    <t>31a45758-10d1-4bd6-b727-2dba0f5d4a63</t>
+  </si>
+  <si>
+    <t>PID 1 (left)</t>
+  </si>
+  <si>
+    <t>ROW-52</t>
+  </si>
+  <si>
+    <t>87f74c7d-2f09-409d-aa8a-83d1925f3839</t>
+  </si>
+  <si>
+    <t>PID 1 (right)</t>
+  </si>
+  <si>
+    <t>ROW-53</t>
+  </si>
+  <si>
+    <t>7519068b-e24e-482d-bfc2-a2c480d725a2</t>
+  </si>
+  <si>
+    <t>PID 1 (back)</t>
+  </si>
+  <si>
+    <t>ROW-54</t>
+  </si>
+  <si>
+    <t>828260f5-0c6a-477f-b917-b0bed1c54a7b</t>
+  </si>
+  <si>
+    <t>PID 1 (back, near H6)</t>
+  </si>
+  <si>
+    <t>ROW-55</t>
+  </si>
+  <si>
+    <t>69c84b19-280a-40f5-aefc-707555609f18</t>
+  </si>
+  <si>
+    <t>ROW-56</t>
+  </si>
+  <si>
+    <t>4f36c94b-b10b-4c30-8d0f-10b4fc18c137</t>
+  </si>
+  <si>
+    <t>PID 3 (left)</t>
+  </si>
+  <si>
+    <t>ROW-57</t>
+  </si>
+  <si>
+    <t>842d4c07-5721-4c86-85ce-d0818a7abe68</t>
+  </si>
+  <si>
+    <t>PID 3 (right)</t>
+  </si>
+  <si>
+    <t>ROW-58</t>
+  </si>
+  <si>
+    <t>27879519-a4d8-43a8-b0a5-08d3ae6c82ab</t>
+  </si>
+  <si>
+    <t>PID 4 (back)</t>
+  </si>
+  <si>
+    <t>ROW-59</t>
+  </si>
+  <si>
+    <t>83b93f5f-cea4-40e4-9bc7-c87aa25c74d6</t>
+  </si>
+  <si>
+    <t>PID 4 (right)</t>
+  </si>
+  <si>
+    <t>ROW-60</t>
+  </si>
+  <si>
+    <t>aeded688-92a4-4553-831b-29eae87f7791</t>
+  </si>
+  <si>
+    <t>PID 5 (right)</t>
+  </si>
+  <si>
+    <t>ROW-61</t>
+  </si>
+  <si>
+    <t>4f7a7d96-4d87-4b11-bebe-8fd24cec5d54</t>
+  </si>
+  <si>
+    <t>PID 6 (right)</t>
+  </si>
+  <si>
+    <t>ROW-62</t>
+  </si>
+  <si>
+    <t>78b05d17-9cf4-49ce-9ed4-3135db93a0aa</t>
+  </si>
+  <si>
+    <t>PID 6 (back)</t>
+  </si>
+  <si>
+    <t>ROW-63</t>
+  </si>
+  <si>
+    <t>5b5b2028-8b18-47a8-aa14-8f58c5c4ee94</t>
+  </si>
+  <si>
+    <t>North Inbound Induct, Presort</t>
+  </si>
+  <si>
+    <t>ROW-64</t>
+  </si>
+  <si>
+    <t>6cf6c845-02f0-4e79-865e-7f100d610ca6</t>
+  </si>
+  <si>
+    <t>North Inbound Induct, PID 2</t>
+  </si>
+  <si>
+    <t>ROW-65</t>
+  </si>
+  <si>
+    <t>6a6efb6c-670b-4472-9604-b9e2aad7b433</t>
+  </si>
+  <si>
+    <t>North Inbound Induct, PID 3</t>
+  </si>
+  <si>
+    <t>ROW-66</t>
+  </si>
+  <si>
+    <t>2a0d1ceb-76a4-4cf8-9830-b1b2b401cec9</t>
+  </si>
+  <si>
+    <t>North Inbound Induct, Gate 10</t>
+  </si>
+  <si>
+    <t>ROW-67</t>
+  </si>
+  <si>
+    <t>a226b97f-8034-4715-927a-cf78e29db288</t>
+  </si>
+  <si>
+    <t>South Inbound Induct, Presort</t>
+  </si>
+  <si>
+    <t>ROW-68</t>
+  </si>
+  <si>
+    <t>18b55138-8a6e-4e9b-b6b6-1dc7764a42bf</t>
+  </si>
+  <si>
+    <t>South Inbound Induct, PID 6</t>
+  </si>
+  <si>
+    <t>ROW-69</t>
+  </si>
+  <si>
+    <t>58dd3900-a434-4f8a-892c-b6132c67e9c7</t>
+  </si>
+  <si>
+    <t>South Inbound Induct, PID 5</t>
+  </si>
+  <si>
+    <t>ROW-70</t>
+  </si>
+  <si>
+    <t>e7806467-7b5c-4229-9c1c-4fd1b34793eb</t>
+  </si>
+  <si>
+    <t>South Inbound Induct, PID 4</t>
+  </si>
+  <si>
+    <t>ROW-71</t>
+  </si>
+  <si>
+    <t>b3b85c5b-4769-4e9a-a4c2-0c02098acab3</t>
+  </si>
+  <si>
+    <t>Under PID Platform</t>
+  </si>
+  <si>
+    <t>ROW-72</t>
+  </si>
+  <si>
+    <t>7e78dae5-f593-47ae-980a-c2d2ce183962</t>
+  </si>
+  <si>
+    <t>RME Cage</t>
+  </si>
+  <si>
+    <t>ROW-73</t>
+  </si>
+  <si>
+    <t>24206c37-f3e7-44b5-ae2e-e0ee58db4b4a</t>
+  </si>
+  <si>
+    <t>Outbound North</t>
+  </si>
+  <si>
+    <t>DD #104</t>
+  </si>
+  <si>
+    <t>ROW-74</t>
+  </si>
+  <si>
+    <t>5b7b3275-aef3-461f-bd40-e699df86dee1</t>
+  </si>
+  <si>
+    <t>ROW-75</t>
+  </si>
+  <si>
+    <t>0f07f88f-d05d-4b67-83b0-75c40db4fe94</t>
+  </si>
+  <si>
+    <t>DD #105</t>
+  </si>
+  <si>
+    <t>ROW-76</t>
+  </si>
+  <si>
+    <t>4738853c-3ed8-4419-8a8c-698a57d650de</t>
+  </si>
+  <si>
+    <t>ROW-77</t>
+  </si>
+  <si>
+    <t>6d37cb85-dff5-47f7-b9a2-376062a3ddd0</t>
+  </si>
+  <si>
+    <t>DD #108</t>
+  </si>
+  <si>
+    <t>ROW-78</t>
+  </si>
+  <si>
+    <t>3b55a08b-165f-4301-b0ef-9e45e8539c26</t>
+  </si>
+  <si>
+    <t>DD #109</t>
+  </si>
+  <si>
+    <t>ROW-79</t>
+  </si>
+  <si>
+    <t>37f83dc4-3730-4198-a546-1e3a0cd91ff8</t>
+  </si>
+  <si>
+    <t>DD #111</t>
+  </si>
+  <si>
+    <t>ROW-80</t>
+  </si>
+  <si>
+    <t>4b265464-adf0-40b4-9274-3abc357a93c4</t>
+  </si>
+  <si>
+    <t>DD #112</t>
+  </si>
+  <si>
+    <t>ROW-81</t>
+  </si>
+  <si>
+    <t>6c1eb851-f380-4d63-9427-7b1f753b69da</t>
+  </si>
+  <si>
+    <t>ROW-82</t>
+  </si>
+  <si>
+    <t>b6422d8b-f9d8-4c23-ac45-5ae3c231eccb</t>
+  </si>
+  <si>
+    <t>DD #115</t>
+  </si>
+  <si>
+    <t>ROW-83</t>
+  </si>
+  <si>
+    <t>027be741-1963-4e28-a0f1-00ade96b5bce</t>
+  </si>
+  <si>
+    <t>ROW-84</t>
+  </si>
+  <si>
+    <t>94ce91af-9215-418c-80d6-a602c34ce6d1</t>
+  </si>
+  <si>
+    <t>DD #116</t>
+  </si>
+  <si>
+    <t>ROW-85</t>
+  </si>
+  <si>
+    <t>b66c8908-3f94-4cf8-9f1b-74647ea054ea</t>
+  </si>
+  <si>
+    <t>DD #118</t>
+  </si>
+  <si>
+    <t>ROW-86</t>
+  </si>
+  <si>
+    <t>2a5974a6-ab4a-447d-bfff-7efa5513b31a</t>
+  </si>
+  <si>
+    <t>DD #119</t>
+  </si>
+  <si>
+    <t>ROW-87</t>
+  </si>
+  <si>
+    <t>96be9fcf-4a45-4794-aa03-f01747149c9f</t>
+  </si>
+  <si>
+    <t>DD #120</t>
+  </si>
+  <si>
+    <t>ROW-88</t>
+  </si>
+  <si>
+    <t>239f5848-62a6-4e29-90a0-9f8b1799b3c5</t>
+  </si>
+  <si>
+    <t>North Jackpot (near quality)</t>
+  </si>
+  <si>
+    <t>ROW-89</t>
+  </si>
+  <si>
+    <t>b58f5cf2-e295-4597-ba40-8f498ba753a7</t>
+  </si>
+  <si>
+    <t>North Jackpot (Green Mile)</t>
+  </si>
+  <si>
+    <t>ROW-90</t>
+  </si>
+  <si>
+    <t>cf41bb67-01ec-466d-ba8c-e8b6fca0be28</t>
+  </si>
+  <si>
+    <t>Non-inventory, DD #127</t>
+  </si>
+  <si>
+    <t>ROW-91</t>
+  </si>
+  <si>
+    <t>a179125b-ae39-41af-bc39-3086390de6ff</t>
+  </si>
+  <si>
+    <t>Outbound South</t>
+  </si>
+  <si>
+    <t>DD #330</t>
+  </si>
+  <si>
+    <t>ROW-92</t>
+  </si>
+  <si>
+    <t>06bb1745-8d7f-4f0b-ab1e-f8deb2c2d5c7</t>
+  </si>
+  <si>
+    <t>DD #336</t>
+  </si>
+  <si>
+    <t>PL 09 (Sort J)</t>
+  </si>
+  <si>
+    <t>87e30b01-797b-477c-bd1d-1a695955d219</t>
+  </si>
+  <si>
+    <t>DD #337</t>
+  </si>
+  <si>
+    <t>ROW-94</t>
+  </si>
+  <si>
+    <t>4e2281af-a726-4d18-b52e-3be16b3a6dfb</t>
+  </si>
+  <si>
+    <t>DD#338</t>
+  </si>
+  <si>
+    <t>PL 46/ OB Deck N</t>
+  </si>
+  <si>
+    <t>ab141b19-531f-4b9b-aabf-892393f1b481</t>
+  </si>
+  <si>
+    <t>DD# 340</t>
+  </si>
+  <si>
+    <t>ROW-96</t>
+  </si>
+  <si>
+    <t>96915a47-1f7b-43e9-8a07-0f163423996c</t>
+  </si>
+  <si>
+    <t>DD#340</t>
+  </si>
+  <si>
+    <t>PL 43/ Man Sort</t>
+  </si>
+  <si>
+    <t>0a07fc39-3714-430f-940e-a3dc1197cfef</t>
+  </si>
+  <si>
+    <t>DD #341</t>
+  </si>
+  <si>
+    <t>PL 21</t>
+  </si>
+  <si>
+    <t>Needs 5S</t>
+  </si>
+  <si>
+    <t>2de8918d-50d9-4a37-9301-72a7a46ede26</t>
+  </si>
+  <si>
+    <t>DD #342</t>
+  </si>
+  <si>
+    <t>ROW-99</t>
+  </si>
+  <si>
+    <t>529e6250-08a2-4033-a46f-aab5933f6347</t>
+  </si>
+  <si>
+    <t>DD#342</t>
+  </si>
+  <si>
+    <t>ROW-100</t>
+  </si>
+  <si>
+    <t>ad6a74fa-3808-4bc4-80a0-9141d78e9777</t>
+  </si>
+  <si>
+    <t>DD #344</t>
+  </si>
+  <si>
+    <t>ROW-101</t>
+  </si>
+  <si>
+    <t>d6323be3-4649-4d63-be9e-e5dfb90bf373</t>
+  </si>
+  <si>
+    <t>DD#344</t>
+  </si>
+  <si>
+    <t>PL27/PID 1 Injection</t>
+  </si>
+  <si>
+    <t>ce4ba9b6-8bc1-46db-9776-56861e0902a9</t>
+  </si>
+  <si>
+    <t>DD #346</t>
+  </si>
+  <si>
+    <t>ROW-103</t>
+  </si>
+  <si>
+    <t>bff3be09-6351-4e33-b4f7-5d9f423b573d</t>
+  </si>
+  <si>
+    <t>DD #347</t>
+  </si>
+  <si>
+    <t>ROW-104</t>
+  </si>
+  <si>
+    <t>84e87e8e-33d1-4c60-89a5-1ca8353f6582</t>
+  </si>
+  <si>
+    <t>DD #348</t>
+  </si>
+  <si>
+    <t>ROW-105</t>
+  </si>
+  <si>
+    <t>390af9f0-a50d-46e3-88aa-6fa0bdb6d703</t>
+  </si>
+  <si>
+    <t>DD#348</t>
+  </si>
+  <si>
+    <t>ROW-106</t>
+  </si>
+  <si>
+    <t>c8f0a93b-c901-4c5b-a261-df976b55468c</t>
+  </si>
+  <si>
+    <t>DD #350</t>
+  </si>
+  <si>
+    <t>ROW-107</t>
+  </si>
+  <si>
+    <t>4e05caae-6997-4ec0-9cf5-27c6d822b5a5</t>
+  </si>
+  <si>
+    <t>DD #351</t>
+  </si>
+  <si>
+    <t>PL 44</t>
+  </si>
+  <si>
+    <t>a3e65b34-240d-4d7b-9e7e-b17114ae20b6</t>
+  </si>
+  <si>
+    <t>DD #352</t>
+  </si>
+  <si>
+    <t>ROW-109</t>
+  </si>
+  <si>
+    <t>2a59108d-a2c6-4517-8dcd-d3f12296d0c7</t>
+  </si>
+  <si>
+    <t>DD#352</t>
+  </si>
+  <si>
+    <t>ROW-110</t>
+  </si>
+  <si>
+    <t>4d947d47-5373-4c05-9321-218fb302fb89</t>
+  </si>
+  <si>
+    <t>Jackpot/ISS</t>
+  </si>
+  <si>
+    <t>ROW-111</t>
+  </si>
+  <si>
+    <t>d1e88038-6d30-4156-997e-28a2f6ec3497</t>
+  </si>
+  <si>
+    <t>Product Awaiting Determination</t>
+  </si>
+  <si>
+    <t>ROW-112</t>
+  </si>
+  <si>
+    <t>2266b86e-c1bd-462d-bccf-676eafc14c23</t>
+  </si>
+  <si>
+    <t>Asset Cage</t>
+  </si>
+  <si>
+    <t>ROW-113</t>
+  </si>
+  <si>
+    <t>62b38b96-8fa7-4925-b8b2-425142b7e3ee</t>
+  </si>
+  <si>
+    <t>Sort</t>
+  </si>
+  <si>
+    <t>Line H</t>
+  </si>
+  <si>
+    <t>ROW-114</t>
+  </si>
+  <si>
+    <t>d63c0216-0ce0-4c24-8a01-906719eb2b3a</t>
+  </si>
+  <si>
+    <t>Line I</t>
+  </si>
+  <si>
+    <t>ROW-115</t>
+  </si>
+  <si>
+    <t>80114c4d-5019-4fd1-892f-f71c75bd6900</t>
+  </si>
+  <si>
+    <t>Line G</t>
+  </si>
+  <si>
+    <t>ROW-116</t>
+  </si>
+  <si>
+    <t>de753200-702f-484f-938b-6268147f5fd3</t>
+  </si>
+  <si>
+    <t>Line E</t>
+  </si>
+  <si>
+    <t>ROW-117</t>
+  </si>
+  <si>
+    <t>029a04f6-6891-4dcb-9446-f07e1dd9e49e</t>
+  </si>
+  <si>
+    <t>Line C</t>
+  </si>
+  <si>
+    <t>ROW-118</t>
+  </si>
+  <si>
+    <t>341acca6-bc99-4e74-96a3-b31d7f89891d</t>
+  </si>
+  <si>
+    <t>ROW-119</t>
+  </si>
+  <si>
+    <t>3bc242c7-2966-455f-b2e4-eb5bf8fc774d</t>
+  </si>
+  <si>
+    <t>Line A</t>
+  </si>
+  <si>
+    <t>ROW-120</t>
+  </si>
+  <si>
+    <t>94f2768e-885a-4a6d-b1d4-eadb93abfaac</t>
+  </si>
+  <si>
+    <t>ROW-121</t>
+  </si>
+  <si>
+    <t>83f917a2-84b1-4d78-9bda-ec7bd48dc0ee</t>
+  </si>
+  <si>
+    <t>Line 1/2</t>
+  </si>
+  <si>
+    <t>ROW-122</t>
+  </si>
+  <si>
+    <t>76b3e08c-ea26-4794-b83e-6f1e391537a3</t>
+  </si>
+  <si>
+    <t>Across from Line 1/2</t>
+  </si>
+  <si>
+    <t>ROW-123</t>
+  </si>
+  <si>
+    <t>148dfbcd-e1ac-4e02-a521-0e4c3333f331</t>
+  </si>
+  <si>
+    <t>UIS 20lbs</t>
+  </si>
+  <si>
+    <t>E 14</t>
+  </si>
+  <si>
+    <t>ROW-124</t>
+  </si>
+  <si>
+    <t>c6196554-5ad3-4aab-a102-68f6f4ea11f4</t>
+  </si>
+  <si>
+    <t>UIS Breezeway</t>
+  </si>
+  <si>
+    <t>159de0af-09fd-4860-8210-ad720b784a30</t>
+  </si>
+  <si>
+    <t>PL03</t>
+  </si>
+  <si>
+    <t>f6b13dc0-da4e-429c-ab1a-415aeef8e410</t>
+  </si>
+  <si>
+    <t>UIS Breezeway, left side</t>
+  </si>
+  <si>
+    <t>PL04/UID</t>
+  </si>
+  <si>
+    <t>1b454a18-35ea-47b6-a415-dc703c70459a</t>
+  </si>
+  <si>
+    <t>ROW-128</t>
+  </si>
+  <si>
+    <t>d3aac8c4-cfc7-4a1b-a332-db4cf134fad8</t>
+  </si>
+  <si>
+    <t>PL 34</t>
+  </si>
+  <si>
+    <t>36337f1e-f878-4792-884c-d115f85de226</t>
+  </si>
+  <si>
+    <t>PL 50/ OB Dock N</t>
+  </si>
+  <si>
+    <t>1a21c020-027a-4597-af0a-d77b53f21a94</t>
+  </si>
+  <si>
+    <t>UIS Breezeway, near OBS</t>
+  </si>
+  <si>
+    <t>ROW-131</t>
+  </si>
+  <si>
+    <t>28d9e3dc-5906-4b1f-bdb1-963a671c446d</t>
+  </si>
+  <si>
+    <t>ROW-132</t>
+  </si>
+  <si>
+    <t>f95d891a-2ffb-44f9-961f-295f52200648</t>
+  </si>
+  <si>
+    <t>End of Line South</t>
+  </si>
+  <si>
+    <t>RP3</t>
+  </si>
+  <si>
+    <t>ROW-133</t>
+  </si>
+  <si>
+    <t>1fadfbd3-0df5-40ea-9883-95c2fe527644</t>
+  </si>
+  <si>
+    <t>RP3, DD#329</t>
+  </si>
+  <si>
+    <t>ROW-134</t>
+  </si>
+  <si>
+    <t>e720b0b2-2ac7-4dda-b120-34828688f814</t>
+  </si>
+  <si>
+    <t>RP2. DD 325</t>
+  </si>
+  <si>
+    <t>ROW-135</t>
+  </si>
+  <si>
+    <t>c3f6b0af-29e1-4381-b39f-34546db0afae</t>
+  </si>
+  <si>
+    <t>Near  RP1/RP2; DD #324</t>
+  </si>
+  <si>
+    <t>ROW-136</t>
+  </si>
+  <si>
+    <t>fa6b5821-16e1-4578-8f3f-d4fe64aa6570</t>
+  </si>
+  <si>
+    <t>RP1</t>
+  </si>
+  <si>
+    <t>ROW-137</t>
+  </si>
+  <si>
+    <t>da66b11b-30cb-4db4-ab69-fd8289157e4c</t>
+  </si>
+  <si>
+    <t>ROW-138</t>
+  </si>
+  <si>
+    <t>b816c520-e860-48f6-bad8-afc98428e6cd</t>
+  </si>
+  <si>
+    <t>MP4</t>
+  </si>
+  <si>
+    <t>ROW-139</t>
+  </si>
+  <si>
+    <t>cb034b0a-ee3f-49f3-b32c-70e26d5c5a81</t>
+  </si>
+  <si>
+    <t>MP1</t>
+  </si>
+  <si>
+    <t>ROW-140</t>
+  </si>
+  <si>
+    <t>3905c688-c704-44e1-bfbc-d51274b38456</t>
+  </si>
+  <si>
+    <t>RPND</t>
+  </si>
+  <si>
+    <t>Line 6</t>
+  </si>
+  <si>
+    <t>PL 14/Line 6</t>
+  </si>
+  <si>
+    <t>12 step</t>
+  </si>
+  <si>
+    <t>93422371-7392-4946-8e8c-239e7d81599c</t>
+  </si>
+  <si>
+    <t>ROW-142</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>reach pole</t>
+  </si>
+  <si>
+    <t>c4ef07fd-43b2-4725-a653-887cab337cfb</t>
+  </si>
+  <si>
+    <t>ROW-143</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>Labelled as jam pole</t>
+  </si>
+  <si>
+    <t>206b5201-e305-43d6-9ca4-76257c0a8881</t>
+  </si>
+  <si>
+    <t>Line 8</t>
+  </si>
+  <si>
+    <t>PL 16/ Line 8</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>Reach pole in holder, holder dangerous</t>
+  </si>
+  <si>
+    <t>ba95b232-6cfd-4ed3-ae5c-82efcb4e281d</t>
+  </si>
+  <si>
+    <t>Line 9</t>
+  </si>
+  <si>
+    <t>PL 17/RPND/Line 8/9</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>19e63cd6-89ab-4940-9c63-f23a7eb1a231</t>
+  </si>
+  <si>
+    <t>PL 15</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>4baaa2f2-9488-4d6f-9921-319d0afcb890</t>
+  </si>
+  <si>
+    <t>Line 14</t>
+  </si>
+  <si>
+    <t>ROW-147</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>521eaaa3-e653-4b54-8d25-d4dbea5c3e3c</t>
+  </si>
+  <si>
+    <t>Line 15</t>
+  </si>
+  <si>
+    <t>ROW-148</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>4765f844-b9ee-473f-a8ff-f66a1a93d847</t>
+  </si>
+  <si>
+    <t>PL 14</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>07a60d8b-aeae-4a87-886a-cc6ead8bdb4f</t>
+  </si>
+  <si>
+    <t>ROW-150</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>fc5cb6ed-4051-4a32-9c52-64a4c446a3c3</t>
+  </si>
+  <si>
+    <t>PL Line I</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>920ce319-7a2c-44bf-a4b0-e7c6fe1345c3</t>
+  </si>
+  <si>
+    <t>ROW-152</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>0d5e020d-53cd-4f78-a748-c668af51ecff</t>
+  </si>
+  <si>
+    <t>Shoe Sorter</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>ROW-153</t>
+  </si>
+  <si>
+    <t>a260fe73-7aac-4ab7-a821-d466a72a8a85</t>
+  </si>
+  <si>
+    <t>ROW-154</t>
+  </si>
+  <si>
+    <t>b5a084ef-dc98-4356-a434-1297f29ddfd4</t>
+  </si>
+  <si>
+    <t>Line 1</t>
+  </si>
+  <si>
+    <t>ROW-155</t>
+  </si>
+  <si>
+    <t>6ef08460-8c93-4630-9f2c-c416f46b066a</t>
+  </si>
+  <si>
+    <t>Line 2</t>
+  </si>
+  <si>
+    <t>ROW-156</t>
+  </si>
+  <si>
+    <t>a2e57413-770e-4cd3-b41b-5253cee1207f</t>
+  </si>
+  <si>
+    <t>Line 3</t>
+  </si>
+  <si>
+    <t>ROW-157</t>
+  </si>
+  <si>
+    <t>ae612a08-da1d-4c3c-9b80-7dc67183ec4e</t>
+  </si>
+  <si>
+    <t>Shoe sorter platform, near curtains</t>
+  </si>
+  <si>
+    <t>ROW-158</t>
+  </si>
+  <si>
+    <t>Pole on steps, 9 steps</t>
+  </si>
+  <si>
+    <t>3212a4c4-f8b8-456d-a583-48f96209f98a</t>
+  </si>
+  <si>
+    <t>Platform: Green mile/UIS</t>
+  </si>
+  <si>
+    <t>ROW-159</t>
+  </si>
+  <si>
+    <t>6719ee06-be35-43ad-b8ec-b76e846ae9f3</t>
+  </si>
+  <si>
+    <t>Platform: Far right on guard rail</t>
+  </si>
+  <si>
+    <t>ROW-160</t>
+  </si>
+  <si>
+    <t>7ce8b671-b35d-4be2-9e94-67cec1510dbc</t>
+  </si>
+  <si>
+    <t>Platform: Jackpot</t>
+  </si>
+  <si>
+    <t>ROW-161</t>
+  </si>
+  <si>
+    <t>6d3c85f3-574f-4d37-954c-529c83ead26a</t>
+  </si>
+  <si>
+    <t>Platform: Cross belt</t>
+  </si>
+  <si>
+    <t>ROW-162</t>
+  </si>
+  <si>
+    <t>ffb70423-ff28-4b12-8b3f-c11d64c0fa4b</t>
+  </si>
+  <si>
+    <t>Platform: near jackpot stairs</t>
+  </si>
+  <si>
+    <t>ROW-163</t>
+  </si>
+  <si>
+    <t>ab85566a-3b9b-49ad-a677-63ed596482e7</t>
+  </si>
+  <si>
+    <t>ROW-164</t>
+  </si>
+  <si>
+    <t>baccc509-c3ee-40bf-a9ac-7a1d3876f81b</t>
+  </si>
+  <si>
+    <t>Platform: near first line</t>
+  </si>
+  <si>
+    <t>ROW-165</t>
+  </si>
+  <si>
+    <t>27d61747-bed6-4499-8677-d1e6f2e4ab4e</t>
+  </si>
+  <si>
+    <t>Platform: middle lane</t>
+  </si>
+  <si>
+    <t>ROW-166</t>
+  </si>
+  <si>
+    <t>Pole is in the chute RME uses to climb</t>
+  </si>
+  <si>
+    <t>ebbbc4b2-1c94-4839-bb95-91df624b50f4</t>
+  </si>
+  <si>
+    <t>H.2 3.3</t>
+  </si>
+  <si>
+    <t>PL 29</t>
+  </si>
+  <si>
+    <t>b626a608-1c49-403c-9ef7-7e16e46ef205</t>
+  </si>
+  <si>
+    <t>H.5 4</t>
+  </si>
+  <si>
+    <t>ROW-168</t>
+  </si>
+  <si>
+    <t>22d7d879-dc94-4e6f-bce7-f6ca31e68edb</t>
+  </si>
+  <si>
+    <t>SR Ops Sign</t>
+  </si>
+  <si>
+    <t>ROW-169</t>
+  </si>
+  <si>
+    <t>814c6b2a-7f1b-4e5a-b52e-dd34e9044ee4</t>
+  </si>
+  <si>
+    <t>H.5 5.2</t>
+  </si>
+  <si>
+    <t>ROW-170</t>
+  </si>
+  <si>
+    <t>fd2adc89-5f1b-4637-a5cc-36a1504b2ff6</t>
+  </si>
+  <si>
+    <t>H.2 5.2</t>
+  </si>
+  <si>
+    <t>ROW-171</t>
+  </si>
+  <si>
+    <t>ea44286c-ee21-405b-91a1-41cecdd5f8eb</t>
+  </si>
+  <si>
+    <t>F. 8 5.2</t>
+  </si>
+  <si>
+    <t>ROW-172</t>
+  </si>
+  <si>
+    <t>92984609-c269-4d7a-9582-0a6ce618cb2b</t>
+  </si>
+  <si>
+    <t>PID Injection 3</t>
+  </si>
+  <si>
+    <t>PL 31</t>
+  </si>
+  <si>
+    <t>fec3acd1-e140-41f7-8215-5b3762b920c1</t>
+  </si>
+  <si>
+    <t>E 7.5 5.2</t>
+  </si>
+  <si>
+    <t>ROW-174</t>
+  </si>
+  <si>
+    <t>841a3c4f-b507-4e20-80f2-fdf821c21cbf</t>
+  </si>
+  <si>
+    <t>DD 213</t>
+  </si>
+  <si>
+    <t>PL 47</t>
+  </si>
+  <si>
+    <t>34a9f273-d46c-492e-b616-eb7902c7bad1</t>
+  </si>
+  <si>
+    <t>D6, see problem solve sign</t>
+  </si>
+  <si>
+    <t>ROW-176</t>
+  </si>
+  <si>
+    <t>1e2d8058-5769-4360-845e-84c88c51d336</t>
+  </si>
+  <si>
+    <t>Across MP 7</t>
+  </si>
+  <si>
+    <t>ROW-177</t>
+  </si>
+  <si>
+    <t>f23d0596-65df-447b-a7e4-940487797cd9</t>
+  </si>
+  <si>
+    <t>ROW-178</t>
+  </si>
+  <si>
+    <t>99d807b9-46d5-4469-94d4-4e18c8897579</t>
+  </si>
+  <si>
+    <t>NPC, E6</t>
+  </si>
+  <si>
+    <t>ROW-179</t>
+  </si>
+  <si>
+    <t>5d3f6096-294a-4bd1-8701-59fde5d81dd9</t>
+  </si>
+  <si>
+    <t>NPC, Problem Solve</t>
+  </si>
+  <si>
+    <t>ROW-180</t>
+  </si>
+  <si>
+    <t>cf83760a-cc54-4471-8a7b-67df02aa5eee</t>
+  </si>
+  <si>
+    <t>ROW-181</t>
+  </si>
+  <si>
+    <t>1a38d41f-aa6e-4f1f-a56d-b63db3798bd5</t>
+  </si>
+  <si>
+    <t>NPC, G6</t>
+  </si>
+  <si>
+    <t>ROW-182</t>
+  </si>
+  <si>
+    <t>0391f088-d1f8-4779-9c58-68566ef320f8</t>
+  </si>
+  <si>
+    <t>Leadership RME</t>
+  </si>
+  <si>
+    <t>ROW-183</t>
+  </si>
+  <si>
+    <t>50da40b3-b4c6-4c10-a198-359a33bfb7ad</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>ROW-184</t>
+  </si>
+  <si>
+    <t>64dc367d-29d0-4f6c-8d34-17160dc28486</t>
+  </si>
+  <si>
+    <t>Line 5</t>
+  </si>
+  <si>
+    <t>ROW-185</t>
+  </si>
+  <si>
+    <t>87a71b45-a357-4352-8286-71ba217718a9</t>
+  </si>
+  <si>
+    <t>ROW-186</t>
+  </si>
+  <si>
+    <t>447a4a7a-8fe4-4620-8fb4-adf8672e6de7</t>
+  </si>
+  <si>
+    <t>ROW-187</t>
+  </si>
+  <si>
+    <t>919b3652-9649-4ba7-9a53-81c3d66a6172</t>
+  </si>
+  <si>
+    <t>ROW-188</t>
+  </si>
+  <si>
+    <t>7f718b18-8881-4fb6-a5af-4243416f16d6</t>
+  </si>
+  <si>
+    <t>ROW-189</t>
+  </si>
+  <si>
+    <t>2e0aea2c-fe73-4e42-bcf8-b39d45fe7e91</t>
+  </si>
+  <si>
+    <t>ROW-190</t>
+  </si>
+  <si>
+    <t>a293adea-82e4-4fad-884a-ae4c75d5b794</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>ROW-191</t>
+  </si>
+  <si>
+    <t>d27257fc-39a5-43f7-883c-dbab26e16c75</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>current-user</t>
+  </si>
+  <si>
+    <t>93422e06-4964-4837-900b-dd417f1751fe</t>
+  </si>
+  <si>
     <t>9f916fa2-0df7-4e45-86f9-bd9fbfeffa5f</t>
-  </si>
-  <si>
-    <t>RWC 5</t>
-  </si>
-  <si>
-    <t>ROW-3</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>bfc5d223-4a44-4713-9be3-f28fd96b8925</t>
-  </si>
-  <si>
-    <t>Cotterman Ladder</t>
-  </si>
-  <si>
-    <t>cotterman</t>
-  </si>
-  <si>
-    <t>ROW-4</t>
-  </si>
-  <si>
-    <t>0111675a-87ae-4c4f-91bd-5db5881dabac</t>
-  </si>
-  <si>
-    <t>RWC 5 Cage</t>
-  </si>
-  <si>
-    <t>ROW-5</t>
-  </si>
-  <si>
-    <t>d019d898-f201-44a9-9f35-999f150a38a9</t>
-  </si>
-  <si>
-    <t>RWC 6</t>
-  </si>
-  <si>
-    <t>ROW-6</t>
-  </si>
-  <si>
-    <t>244d6e71-ce77-4ff8-b9a9-69c8f2cebb01</t>
-  </si>
-  <si>
-    <t>ROW-7</t>
-  </si>
-  <si>
-    <t>2d7693e6-098e-4752-baa5-685edbad3e2d</t>
-  </si>
-  <si>
-    <t>RWC 6 cage</t>
-  </si>
-  <si>
-    <t>ROW-8</t>
-  </si>
-  <si>
-    <t>0ac8a751-6d43-46b4-a098-8facf024c131</t>
-  </si>
-  <si>
-    <t>MP 8</t>
-  </si>
-  <si>
-    <t>ROW-9</t>
-  </si>
-  <si>
-    <t>1515e66f-80b5-4848-bf7d-4551f9ad977b</t>
-  </si>
-  <si>
-    <t>MP 7</t>
-  </si>
-  <si>
-    <t>ROW-10</t>
-  </si>
-  <si>
-    <t>slight_bend</t>
-  </si>
-  <si>
-    <t>e7752cf2-c641-43fd-9527-6ca4a0427d0f</t>
-  </si>
-  <si>
-    <t>MP 7 (across from it)</t>
-  </si>
-  <si>
-    <t>ROW-11</t>
-  </si>
-  <si>
-    <t>48019e0a-eb08-42df-96f5-5cde39a735bf</t>
-  </si>
-  <si>
-    <t>Green Mile (DD 145)</t>
-  </si>
-  <si>
-    <t>ROW-12</t>
-  </si>
-  <si>
-    <t>49f2a9bb-d1df-42f3-a12a-81fb0ebdd376</t>
-  </si>
-  <si>
-    <t>Inbound</t>
-  </si>
-  <si>
-    <t>Far out past PID1</t>
-  </si>
-  <si>
-    <t>Mezzanine</t>
-  </si>
-  <si>
-    <t>ROW-13</t>
-  </si>
-  <si>
-    <t>d81619ef-2b49-4006-9422-cdf50fd04708</t>
-  </si>
-  <si>
-    <t>PID 1</t>
-  </si>
-  <si>
-    <t>ROW-14</t>
-  </si>
-  <si>
-    <t>948a2146-8dea-4379-a8bd-a9c01f3cba80</t>
-  </si>
-  <si>
-    <t>PID 2</t>
-  </si>
-  <si>
-    <t>ROW-15</t>
-  </si>
-  <si>
-    <t>802616b4-e600-45ee-9466-604b915e2a58</t>
-  </si>
-  <si>
-    <t>PID 3</t>
-  </si>
-  <si>
-    <t>ROW-16</t>
-  </si>
-  <si>
-    <t>9f38b248-2a67-4416-9951-b0f59b7fc73b</t>
-  </si>
-  <si>
-    <t>PID 4</t>
-  </si>
-  <si>
-    <t>ROW-17</t>
-  </si>
-  <si>
-    <t>539a12be-2f1e-44f5-bfd6-d13a718d4249</t>
-  </si>
-  <si>
-    <t>PID 5</t>
-  </si>
-  <si>
-    <t>ROW-18</t>
-  </si>
-  <si>
-    <t>311d4fdf-3d1f-4920-8dfa-6e06b6d0bf00</t>
-  </si>
-  <si>
-    <t>PID 6</t>
-  </si>
-  <si>
-    <t>ROW-19</t>
-  </si>
-  <si>
-    <t>ae74bc8c-f116-429a-8b6b-d9103e644dd1</t>
-  </si>
-  <si>
-    <t>DD #211</t>
-  </si>
-  <si>
-    <t>ROW-20</t>
-  </si>
-  <si>
-    <t>20e0cd0a-7053-4c93-911f-2070bbd7e99b</t>
-  </si>
-  <si>
-    <t>ROW-21</t>
-  </si>
-  <si>
-    <t>6490a947-f2f1-4436-8757-cd0bcd1b1674</t>
-  </si>
-  <si>
-    <t>DD #212/ E3</t>
-  </si>
-  <si>
-    <t>ROW-22</t>
-  </si>
-  <si>
-    <t>15a329cb-a426-4b71-9e14-c94bc1bd8096</t>
-  </si>
-  <si>
-    <t>DD 212, near PID platform</t>
-  </si>
-  <si>
-    <t>ROW-23</t>
-  </si>
-  <si>
-    <t>79e7ba7a-98b1-46ce-9441-af4c15ef9c52</t>
-  </si>
-  <si>
-    <t>PID Injection 4</t>
-  </si>
-  <si>
-    <t>PL 38</t>
-  </si>
-  <si>
-    <t>Fastener coming loose</t>
-  </si>
-  <si>
-    <t>e86bb649-4a32-4364-a1df-49de53657ca2</t>
-  </si>
-  <si>
-    <t>DD #212</t>
-  </si>
-  <si>
-    <t>ROW-25</t>
-  </si>
-  <si>
-    <t>c67f1232-173d-42ee-9c8b-4d60af1fcdd9</t>
-  </si>
-  <si>
-    <t>DD #213</t>
-  </si>
-  <si>
-    <t>ROW-26</t>
-  </si>
-  <si>
-    <t>Should this be moved sides</t>
-  </si>
-  <si>
-    <t>ac1add07-9857-4bcf-9f0a-b2e0931033a2</t>
-  </si>
-  <si>
-    <t>ROW-27</t>
-  </si>
-  <si>
-    <t>27ba0afa-fe5b-4012-ac56-a54129318ca9</t>
-  </si>
-  <si>
-    <t>DD #214</t>
-  </si>
-  <si>
-    <t>ROW-28</t>
-  </si>
-  <si>
-    <t>76d20c41-06e2-4d9e-9200-a462ed427347</t>
-  </si>
-  <si>
-    <t>PL- PID 5</t>
-  </si>
-  <si>
-    <t>15 step</t>
-  </si>
-  <si>
-    <t>71658ba9-fde3-41c0-8077-e42cfa0bf96d</t>
-  </si>
-  <si>
-    <t>ROW-30</t>
-  </si>
-  <si>
-    <t>73aff56f-9a06-455f-96b4-8cfe180d31d6</t>
-  </si>
-  <si>
-    <t>PL Inbound Dock</t>
-  </si>
-  <si>
-    <t>cd10a918-7cf4-4c5a-901b-8a735ad5a69f</t>
-  </si>
-  <si>
-    <t>DD #215</t>
-  </si>
-  <si>
-    <t>ROW-32</t>
-  </si>
-  <si>
-    <t>a2ac979c-b460-457b-8d35-2003d418fa42</t>
-  </si>
-  <si>
-    <t>Dd #215</t>
-  </si>
-  <si>
-    <t>PL-, PID 5</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Pole on steps</t>
-  </si>
-  <si>
-    <t>a954088a-068a-4aac-a518-afc523f343e6</t>
-  </si>
-  <si>
-    <t>ROW-34</t>
-  </si>
-  <si>
-    <t>546dc12d-2a7d-495b-a2cb-88f14b11d6de</t>
-  </si>
-  <si>
-    <t>ROW-35</t>
-  </si>
-  <si>
-    <t>Needs ID</t>
-  </si>
-  <si>
-    <t>0a157eed-ce90-453f-9ffa-8dd25e17d30b</t>
-  </si>
-  <si>
-    <t>DD #216</t>
-  </si>
-  <si>
-    <t>ROW-36</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>ed2808a8-7ccf-4ce7-aa3e-d95f28187f09</t>
-  </si>
-  <si>
-    <t>PL-, PID 3</t>
-  </si>
-  <si>
-    <t>2df43077-910b-4d33-94d5-111923ebbaa1</t>
-  </si>
-  <si>
-    <t>DD #217</t>
-  </si>
-  <si>
-    <t>ROW-38</t>
-  </si>
-  <si>
-    <t>cdd2504e-b0c6-419f-a071-4b4d4cf112dd</t>
-  </si>
-  <si>
-    <t>DD #218</t>
-  </si>
-  <si>
-    <t>ROW-39</t>
-  </si>
-  <si>
-    <t>dd8434ce-017d-4e5b-9867-29bdffa3c792</t>
-  </si>
-  <si>
-    <t>ROW-40</t>
-  </si>
-  <si>
-    <t>b0ee1914-0b0a-4fcb-a114-da4e8c630346</t>
-  </si>
-  <si>
-    <t>PL 20, Line 4</t>
-  </si>
-  <si>
-    <t>274738c5-ba0b-499f-b379-0228960c326b</t>
-  </si>
-  <si>
-    <t>DD #219</t>
-  </si>
-  <si>
-    <t>ROW-42</t>
-  </si>
-  <si>
-    <t>ba609d39-c3dc-4621-8ca5-1d0f1e6116f3</t>
-  </si>
-  <si>
-    <t>DD #220</t>
-  </si>
-  <si>
-    <t>ROW-43</t>
-  </si>
-  <si>
-    <t>d8b2ee41-2a8f-4b0c-b40b-8074928baf8a</t>
-  </si>
-  <si>
-    <t>ROW-44</t>
-  </si>
-  <si>
-    <t>d00bfc16-dbd1-4945-a024-cb62f089e1eb</t>
-  </si>
-  <si>
-    <t>PL 24/IB Dock</t>
-  </si>
-  <si>
-    <t>afb2cd45-bd0b-4d70-b895-3c8e671541ac</t>
-  </si>
-  <si>
-    <t>DD #221</t>
-  </si>
-  <si>
-    <t>ROW-46</t>
-  </si>
-  <si>
-    <t>e99da653-6753-41bc-a1e4-7d4e544f615f</t>
-  </si>
-  <si>
-    <t>DD #221, merge</t>
-  </si>
-  <si>
-    <t>ROW-47</t>
-  </si>
-  <si>
-    <t>ae353c04-0628-4b47-b82d-304614cb8c48</t>
-  </si>
-  <si>
-    <t>PL PID 1</t>
-  </si>
-  <si>
-    <t>17290be0-da0b-4207-b791-d54c84cf3013</t>
-  </si>
-  <si>
-    <t>DD  221</t>
-  </si>
-  <si>
-    <t>PL 36</t>
-  </si>
-  <si>
-    <t>7 step ladder</t>
-  </si>
-  <si>
-    <t>041b538e-5f6f-41fc-8dd7-73e2102cc999</t>
-  </si>
-  <si>
-    <t>Line 11</t>
-  </si>
-  <si>
-    <t>ROW-50</t>
-  </si>
-  <si>
-    <t>13373bf7-e406-43ec-b2ef-5a620428463c</t>
-  </si>
-  <si>
-    <t>DD #222</t>
-  </si>
-  <si>
-    <t>ROW-51</t>
-  </si>
-  <si>
-    <t>8bee7eb5-b9d3-4829-9c19-268b9d00bf54</t>
-  </si>
-  <si>
-    <t>PID 1 (left)</t>
-  </si>
-  <si>
-    <t>ROW-52</t>
-  </si>
-  <si>
-    <t>2ffbb5ef-25de-4854-9592-d7c762a84f23</t>
-  </si>
-  <si>
-    <t>PID 1 (right)</t>
-  </si>
-  <si>
-    <t>ROW-53</t>
-  </si>
-  <si>
-    <t>8b999d80-1510-43a7-a447-8bfc7fbfe743</t>
-  </si>
-  <si>
-    <t>PID 1 (back)</t>
-  </si>
-  <si>
-    <t>ROW-54</t>
-  </si>
-  <si>
-    <t>2d2ccc72-3b58-45eb-82a2-01f954661c79</t>
-  </si>
-  <si>
-    <t>PID 1 (back, near H6)</t>
-  </si>
-  <si>
-    <t>ROW-55</t>
-  </si>
-  <si>
-    <t>51ec8712-40c9-4e3e-8eec-c4d4de86ff61</t>
-  </si>
-  <si>
-    <t>ROW-56</t>
-  </si>
-  <si>
-    <t>491fbdeb-ef3f-4760-87fe-86329b646ee7</t>
-  </si>
-  <si>
-    <t>PID 3 (left)</t>
-  </si>
-  <si>
-    <t>ROW-57</t>
-  </si>
-  <si>
-    <t>301d37b4-9c38-4b4e-9a80-0d5fbc990e87</t>
-  </si>
-  <si>
-    <t>PID 3 (right)</t>
-  </si>
-  <si>
-    <t>ROW-58</t>
-  </si>
-  <si>
-    <t>bce4061e-f5ef-4557-af27-5a2b288c8664</t>
-  </si>
-  <si>
-    <t>PID 4 (back)</t>
-  </si>
-  <si>
-    <t>ROW-59</t>
-  </si>
-  <si>
-    <t>049f97c3-ec05-49a2-814c-8da610b6e1e4</t>
-  </si>
-  <si>
-    <t>PID 4 (right)</t>
-  </si>
-  <si>
-    <t>ROW-60</t>
-  </si>
-  <si>
-    <t>417a8c7d-6c94-4f48-bc47-2e3e6ced3c44</t>
-  </si>
-  <si>
-    <t>PID 5 (right)</t>
-  </si>
-  <si>
-    <t>ROW-61</t>
-  </si>
-  <si>
-    <t>aca67347-1e75-4244-99ca-5d728c3bc99e</t>
-  </si>
-  <si>
-    <t>PID 6 (right)</t>
-  </si>
-  <si>
-    <t>ROW-62</t>
-  </si>
-  <si>
-    <t>a67b5541-553e-4ea6-9471-d16879704595</t>
-  </si>
-  <si>
-    <t>PID 6 (back)</t>
-  </si>
-  <si>
-    <t>ROW-63</t>
-  </si>
-  <si>
-    <t>be4b9018-965a-405b-b1fe-0ff92d1e0d7b</t>
-  </si>
-  <si>
-    <t>North Inbound Induct, Presort</t>
-  </si>
-  <si>
-    <t>ROW-64</t>
-  </si>
-  <si>
-    <t>194db6bf-11c3-4cda-807b-4bcbe3951ddf</t>
-  </si>
-  <si>
-    <t>North Inbound Induct, PID 2</t>
-  </si>
-  <si>
-    <t>ROW-65</t>
-  </si>
-  <si>
-    <t>61c955ce-c160-4cd9-a2fb-5cbe8a66dcab</t>
-  </si>
-  <si>
-    <t>North Inbound Induct, PID 3</t>
-  </si>
-  <si>
-    <t>ROW-66</t>
-  </si>
-  <si>
-    <t>c47ab850-5fd0-413d-8a16-5bbd205e3ad0</t>
-  </si>
-  <si>
-    <t>North Inbound Induct, Gate 10</t>
-  </si>
-  <si>
-    <t>ROW-67</t>
-  </si>
-  <si>
-    <t>42b7917f-39d7-4008-aea3-2e644b736efe</t>
-  </si>
-  <si>
-    <t>South Inbound Induct, Presort</t>
-  </si>
-  <si>
-    <t>ROW-68</t>
-  </si>
-  <si>
-    <t>c40e23e4-692a-43b4-8c4d-4489f4c3aef9</t>
-  </si>
-  <si>
-    <t>South Inbound Induct, PID 6</t>
-  </si>
-  <si>
-    <t>ROW-69</t>
-  </si>
-  <si>
-    <t>86d0a651-5429-4775-af12-890c7beb4ed6</t>
-  </si>
-  <si>
-    <t>South Inbound Induct, PID 5</t>
-  </si>
-  <si>
-    <t>ROW-70</t>
-  </si>
-  <si>
-    <t>ac59ce26-8a1e-4c68-bae5-148348306bd6</t>
-  </si>
-  <si>
-    <t>South Inbound Induct, PID 4</t>
-  </si>
-  <si>
-    <t>ROW-71</t>
-  </si>
-  <si>
-    <t>4bb9bdc8-b2f8-428a-b045-1c5bc070721d</t>
-  </si>
-  <si>
-    <t>Under PID Platform</t>
-  </si>
-  <si>
-    <t>ROW-72</t>
-  </si>
-  <si>
-    <t>511e58bf-2a99-49b9-b3e0-ea055dedfcce</t>
-  </si>
-  <si>
-    <t>RME Cage</t>
-  </si>
-  <si>
-    <t>ROW-73</t>
-  </si>
-  <si>
-    <t>83cf3d9f-4084-4acc-aaa9-92067e7435e0</t>
-  </si>
-  <si>
-    <t>Outbound North</t>
-  </si>
-  <si>
-    <t>DD #104</t>
-  </si>
-  <si>
-    <t>ROW-74</t>
-  </si>
-  <si>
-    <t>1025f2dd-1727-4eae-a890-d54e49207674</t>
-  </si>
-  <si>
-    <t>ROW-75</t>
-  </si>
-  <si>
-    <t>a9afee6f-e8f0-4deb-8e07-dd45a95ed4d3</t>
-  </si>
-  <si>
-    <t>DD #105</t>
-  </si>
-  <si>
-    <t>ROW-76</t>
-  </si>
-  <si>
-    <t>ca03bd03-e975-44ed-a7d7-965cd381ba9e</t>
-  </si>
-  <si>
-    <t>ROW-77</t>
-  </si>
-  <si>
-    <t>3f880e7b-ef5f-4d7b-885b-39f97939676e</t>
-  </si>
-  <si>
-    <t>DD #108</t>
-  </si>
-  <si>
-    <t>ROW-78</t>
-  </si>
-  <si>
-    <t>96ffe6ee-da1e-4347-9cf9-4601537cbe89</t>
-  </si>
-  <si>
-    <t>DD #109</t>
-  </si>
-  <si>
-    <t>ROW-79</t>
-  </si>
-  <si>
-    <t>702b2fec-6fc0-4921-b72a-0511a4a5edb5</t>
-  </si>
-  <si>
-    <t>DD #111</t>
-  </si>
-  <si>
-    <t>ROW-80</t>
-  </si>
-  <si>
-    <t>7d649a7d-59a4-4023-99a5-626cc1b558be</t>
-  </si>
-  <si>
-    <t>DD #112</t>
-  </si>
-  <si>
-    <t>ROW-81</t>
-  </si>
-  <si>
-    <t>c7cb0783-47de-4835-9b7b-c90f3a4a39f3</t>
-  </si>
-  <si>
-    <t>ROW-82</t>
-  </si>
-  <si>
-    <t>b0846d27-9515-4818-92e8-f650c6609a57</t>
-  </si>
-  <si>
-    <t>DD #115</t>
-  </si>
-  <si>
-    <t>ROW-83</t>
-  </si>
-  <si>
-    <t>79632b0d-4476-4843-a689-f5c5bfe70728</t>
-  </si>
-  <si>
-    <t>ROW-84</t>
-  </si>
-  <si>
-    <t>44d0040e-bea1-4bd6-a1b2-67af36cfc213</t>
-  </si>
-  <si>
-    <t>DD #116</t>
-  </si>
-  <si>
-    <t>ROW-85</t>
-  </si>
-  <si>
-    <t>0dc8ad6d-f7ca-4c23-ad57-ac89565fb4c6</t>
-  </si>
-  <si>
-    <t>DD #118</t>
-  </si>
-  <si>
-    <t>ROW-86</t>
-  </si>
-  <si>
-    <t>64b311ca-6736-4eed-bc7f-29b6cf1aa945</t>
-  </si>
-  <si>
-    <t>DD #119</t>
-  </si>
-  <si>
-    <t>ROW-87</t>
-  </si>
-  <si>
-    <t>448cb110-9ae1-4e0b-b7dc-59d251fff532</t>
-  </si>
-  <si>
-    <t>DD #120</t>
-  </si>
-  <si>
-    <t>ROW-88</t>
-  </si>
-  <si>
-    <t>3862ba5c-1a86-41ca-8016-12129a0bcc4c</t>
-  </si>
-  <si>
-    <t>North Jackpot (near quality)</t>
-  </si>
-  <si>
-    <t>ROW-89</t>
-  </si>
-  <si>
-    <t>18a0ae92-c41d-4614-aea2-18f1923b2278</t>
-  </si>
-  <si>
-    <t>North Jackpot (Green Mile)</t>
-  </si>
-  <si>
-    <t>ROW-90</t>
-  </si>
-  <si>
-    <t>e4fcf5f7-2951-474c-9fe7-9c3958c10dd0</t>
-  </si>
-  <si>
-    <t>Non-inventory, DD #127</t>
-  </si>
-  <si>
-    <t>ROW-91</t>
-  </si>
-  <si>
-    <t>c9605e35-b869-4a9f-962a-e7bb1e13bac2</t>
-  </si>
-  <si>
-    <t>Outbound South</t>
-  </si>
-  <si>
-    <t>DD #330</t>
-  </si>
-  <si>
-    <t>ROW-92</t>
-  </si>
-  <si>
-    <t>8180a6b3-d1fd-4320-ae13-db4c75d2f8a5</t>
-  </si>
-  <si>
-    <t>DD #336</t>
-  </si>
-  <si>
-    <t>PL 09 (Sort J)</t>
-  </si>
-  <si>
-    <t>3dc399e6-f955-43ce-9340-f55f6726d65f</t>
-  </si>
-  <si>
-    <t>DD #337</t>
-  </si>
-  <si>
-    <t>ROW-94</t>
-  </si>
-  <si>
-    <t>6e3a18dd-acdb-4acd-8f5d-d2071ee65918</t>
-  </si>
-  <si>
-    <t>DD#338</t>
-  </si>
-  <si>
-    <t>PL 46/ OB Deck N</t>
-  </si>
-  <si>
-    <t>51b4cf9a-4f70-4f90-951e-1242f7ff46aa</t>
-  </si>
-  <si>
-    <t>DD# 340</t>
-  </si>
-  <si>
-    <t>ROW-96</t>
-  </si>
-  <si>
-    <t>297cf3f4-96b9-486d-8be4-a2f963f63739</t>
-  </si>
-  <si>
-    <t>DD#340</t>
-  </si>
-  <si>
-    <t>PL 43/ Man Sort</t>
-  </si>
-  <si>
-    <t>42ffce91-9e71-4ff8-8253-e3dc8be43f81</t>
-  </si>
-  <si>
-    <t>DD #341</t>
-  </si>
-  <si>
-    <t>PL 21</t>
-  </si>
-  <si>
-    <t>Needs 5S</t>
-  </si>
-  <si>
-    <t>edd8405f-bcb8-489e-bf09-e220d9e3dd35</t>
-  </si>
-  <si>
-    <t>DD #342</t>
-  </si>
-  <si>
-    <t>ROW-99</t>
-  </si>
-  <si>
-    <t>16e34df0-d981-409f-acb2-96c00c733144</t>
-  </si>
-  <si>
-    <t>DD#342</t>
-  </si>
-  <si>
-    <t>ROW-100</t>
-  </si>
-  <si>
-    <t>0f3feed6-31e0-4398-8790-43ffddc5cb50</t>
-  </si>
-  <si>
-    <t>DD #344</t>
-  </si>
-  <si>
-    <t>ROW-101</t>
-  </si>
-  <si>
-    <t>228bff33-afaf-4ff5-954e-aa57eda6de1b</t>
-  </si>
-  <si>
-    <t>DD#344</t>
-  </si>
-  <si>
-    <t>PL27/PID 1 Injection</t>
-  </si>
-  <si>
-    <t>93229e2c-5c83-4f0b-a864-9e3694196126</t>
-  </si>
-  <si>
-    <t>DD #346</t>
-  </si>
-  <si>
-    <t>ROW-103</t>
-  </si>
-  <si>
-    <t>4d2aaf09-d983-48c6-9a89-45007dd77094</t>
-  </si>
-  <si>
-    <t>DD #347</t>
-  </si>
-  <si>
-    <t>ROW-104</t>
-  </si>
-  <si>
-    <t>9578bf52-17d8-46e7-9247-dc73c674dfb0</t>
-  </si>
-  <si>
-    <t>DD #348</t>
-  </si>
-  <si>
-    <t>ROW-105</t>
-  </si>
-  <si>
-    <t>27dd115d-6cb3-4a72-aadf-0fedcac3e5d4</t>
-  </si>
-  <si>
-    <t>DD#348</t>
-  </si>
-  <si>
-    <t>ROW-106</t>
-  </si>
-  <si>
-    <t>4e512509-4d64-4e30-82ef-e9c86f9f7a70</t>
-  </si>
-  <si>
-    <t>DD #350</t>
-  </si>
-  <si>
-    <t>ROW-107</t>
-  </si>
-  <si>
-    <t>a225ad9e-d54a-4e33-8d05-1f6680222a84</t>
-  </si>
-  <si>
-    <t>DD #351</t>
-  </si>
-  <si>
-    <t>PL 44</t>
-  </si>
-  <si>
-    <t>ac1a88a2-0e56-40e2-a863-fcc12373951c</t>
-  </si>
-  <si>
-    <t>DD #352</t>
-  </si>
-  <si>
-    <t>ROW-109</t>
-  </si>
-  <si>
-    <t>4f451759-c640-437c-9833-7e23030a99f1</t>
-  </si>
-  <si>
-    <t>DD#352</t>
-  </si>
-  <si>
-    <t>ROW-110</t>
-  </si>
-  <si>
-    <t>5676c957-2e23-4955-b236-ac72e20a2fa4</t>
-  </si>
-  <si>
-    <t>Jackpot/ISS</t>
-  </si>
-  <si>
-    <t>ROW-111</t>
-  </si>
-  <si>
-    <t>88e81488-0899-4656-bb15-84c7f6305cbd</t>
-  </si>
-  <si>
-    <t>Product Awaiting Determination</t>
-  </si>
-  <si>
-    <t>ROW-112</t>
-  </si>
-  <si>
-    <t>690e64ae-b4b0-418e-9791-8e75d86ccc2a</t>
-  </si>
-  <si>
-    <t>Asset Cage</t>
-  </si>
-  <si>
-    <t>ROW-113</t>
-  </si>
-  <si>
-    <t>2456f60a-8cf1-485b-af0b-181d78c51107</t>
-  </si>
-  <si>
-    <t>Sort</t>
-  </si>
-  <si>
-    <t>Line H</t>
-  </si>
-  <si>
-    <t>ROW-114</t>
-  </si>
-  <si>
-    <t>7c498a08-7ad8-4be0-a31f-8c71f6a3d84f</t>
-  </si>
-  <si>
-    <t>Line I</t>
-  </si>
-  <si>
-    <t>ROW-115</t>
-  </si>
-  <si>
-    <t>a9899305-e20d-4af5-a606-215c9cb87235</t>
-  </si>
-  <si>
-    <t>Line G</t>
-  </si>
-  <si>
-    <t>ROW-116</t>
-  </si>
-  <si>
-    <t>4048fc83-5ade-420d-9797-1034e950388f</t>
-  </si>
-  <si>
-    <t>Line E</t>
-  </si>
-  <si>
-    <t>ROW-117</t>
-  </si>
-  <si>
-    <t>4b3bdba2-6d08-4518-9189-1340ca2f230e</t>
-  </si>
-  <si>
-    <t>Line C</t>
-  </si>
-  <si>
-    <t>ROW-118</t>
-  </si>
-  <si>
-    <t>a81e181c-6b8f-420c-b3d0-a1a7a39c1f80</t>
-  </si>
-  <si>
-    <t>ROW-119</t>
-  </si>
-  <si>
-    <t>f220b3ba-6b9b-4248-976c-9dfd33bce68b</t>
-  </si>
-  <si>
-    <t>Line A</t>
-  </si>
-  <si>
-    <t>ROW-120</t>
-  </si>
-  <si>
-    <t>9a6601f2-024d-4095-9b5d-5cd0049cb250</t>
-  </si>
-  <si>
-    <t>ROW-121</t>
-  </si>
-  <si>
-    <t>12894ac5-05e1-492e-8f80-58fdc0d4bb3f</t>
-  </si>
-  <si>
-    <t>Line 1/2</t>
-  </si>
-  <si>
-    <t>ROW-122</t>
-  </si>
-  <si>
-    <t>91ff2807-2dd8-41ca-91d9-4483e540fef7</t>
-  </si>
-  <si>
-    <t>Across from Line 1/2</t>
-  </si>
-  <si>
-    <t>ROW-123</t>
-  </si>
-  <si>
-    <t>4bbe802c-e4bc-4bba-95ab-227cc2e93aa0</t>
-  </si>
-  <si>
-    <t>UIS 20lbs</t>
-  </si>
-  <si>
-    <t>E 14</t>
-  </si>
-  <si>
-    <t>ROW-124</t>
-  </si>
-  <si>
-    <t>4f1ce1d2-74f8-42f8-ada8-1365c6bacce7</t>
-  </si>
-  <si>
-    <t>UIS Breezeway</t>
-  </si>
-  <si>
-    <t>9a3bb021-af4f-4b3c-bd86-946dbf424d09</t>
-  </si>
-  <si>
-    <t>PL03</t>
-  </si>
-  <si>
-    <t>71013123-5fc9-4d88-ae28-8dee908f5dc6</t>
-  </si>
-  <si>
-    <t>UIS Breezeway, left side</t>
-  </si>
-  <si>
-    <t>PL04/UID</t>
-  </si>
-  <si>
-    <t>1c399ffa-0632-40dc-8778-dbc7d4ab1c7b</t>
-  </si>
-  <si>
-    <t>ROW-128</t>
-  </si>
-  <si>
-    <t>eab0ae09-f2e8-44bc-8755-74c3ca614bda</t>
-  </si>
-  <si>
-    <t>PL 34</t>
-  </si>
-  <si>
-    <t>70ca98c6-95eb-4d44-83eb-5234059b3c50</t>
-  </si>
-  <si>
-    <t>PL 50/ OB Dock N</t>
-  </si>
-  <si>
-    <t>975ef3fa-1679-4b02-af05-13a29e2969dc</t>
-  </si>
-  <si>
-    <t>UIS Breezeway, near OBS</t>
-  </si>
-  <si>
-    <t>ROW-131</t>
-  </si>
-  <si>
-    <t>5a69a3a2-2b8b-4d75-80a3-969fc63a6f41</t>
-  </si>
-  <si>
-    <t>ROW-132</t>
-  </si>
-  <si>
-    <t>0f739082-36ec-43ea-815c-67265b9a8a5e</t>
-  </si>
-  <si>
-    <t>End of Line South</t>
-  </si>
-  <si>
-    <t>RP3</t>
-  </si>
-  <si>
-    <t>ROW-133</t>
-  </si>
-  <si>
-    <t>cc7fe22f-6b98-4a5e-bd0b-948f1c8d5283</t>
-  </si>
-  <si>
-    <t>RP3, DD#329</t>
-  </si>
-  <si>
-    <t>ROW-134</t>
-  </si>
-  <si>
-    <t>9a2da81a-ea16-4c46-88db-fe5d39e42a69</t>
-  </si>
-  <si>
-    <t>RP2. DD 325</t>
-  </si>
-  <si>
-    <t>ROW-135</t>
-  </si>
-  <si>
-    <t>637979dd-9de6-439b-9d91-e5de50a800b5</t>
-  </si>
-  <si>
-    <t>Near  RP1/RP2; DD #324</t>
-  </si>
-  <si>
-    <t>ROW-136</t>
-  </si>
-  <si>
-    <t>ee7d1530-c5ee-4484-b758-1008b17ded22</t>
-  </si>
-  <si>
-    <t>RP1</t>
-  </si>
-  <si>
-    <t>ROW-137</t>
-  </si>
-  <si>
-    <t>3356c15a-af11-4b03-bc07-a0f6e4e16b5a</t>
-  </si>
-  <si>
-    <t>ROW-138</t>
-  </si>
-  <si>
-    <t>28ff06ef-d94d-4bdb-a154-a3575a70e210</t>
-  </si>
-  <si>
-    <t>MP4</t>
-  </si>
-  <si>
-    <t>ROW-139</t>
-  </si>
-  <si>
-    <t>9ee45198-1eeb-4d0a-abd1-d184e81bb7f3</t>
-  </si>
-  <si>
-    <t>MP1</t>
-  </si>
-  <si>
-    <t>ROW-140</t>
-  </si>
-  <si>
-    <t>f91e2587-013d-49b9-9a84-1d4893146682</t>
-  </si>
-  <si>
-    <t>RPND</t>
-  </si>
-  <si>
-    <t>Line 6</t>
-  </si>
-  <si>
-    <t>PL 14/Line 6</t>
-  </si>
-  <si>
-    <t>12 step</t>
-  </si>
-  <si>
-    <t>4dda3922-736a-4bfa-a94b-c040c4483d4d</t>
-  </si>
-  <si>
-    <t>ROW-142</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>reach pole</t>
-  </si>
-  <si>
-    <t>9b1444cf-fe43-473e-b8ad-2f3b305bbcd9</t>
-  </si>
-  <si>
-    <t>ROW-143</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>Labelled as jam pole</t>
-  </si>
-  <si>
-    <t>a777ffd6-402e-4d5c-84dc-78322623483d</t>
-  </si>
-  <si>
-    <t>Line 8</t>
-  </si>
-  <si>
-    <t>PL 16/ Line 8</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>Reach pole in holder, holder dangerous</t>
-  </si>
-  <si>
-    <t>a38a4cb4-c784-4934-8d7c-a34d1be79090</t>
-  </si>
-  <si>
-    <t>Line 9</t>
-  </si>
-  <si>
-    <t>PL 17/RPND/Line 8/9</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>6d1b43bb-4e66-4934-ba5e-bedbf0661789</t>
-  </si>
-  <si>
-    <t>PL 15</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>c3da37c2-ca93-4087-a463-a299af979140</t>
-  </si>
-  <si>
-    <t>Line 14</t>
-  </si>
-  <si>
-    <t>ROW-147</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>f9833ece-32e1-476d-be12-f76d03f42539</t>
-  </si>
-  <si>
-    <t>Line 15</t>
-  </si>
-  <si>
-    <t>ROW-148</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>1268c701-a16a-449d-a356-d099e9ef3c5e</t>
-  </si>
-  <si>
-    <t>PL 14</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>cbb91a09-a81e-4dee-bc56-6bbaaee2ea15</t>
-  </si>
-  <si>
-    <t>ROW-150</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>3eaef89b-b1aa-44d5-81f5-83dca4653825</t>
-  </si>
-  <si>
-    <t>PL Line I</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>f70d6274-2074-4b60-9653-5d67d37b4800</t>
-  </si>
-  <si>
-    <t>ROW-152</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>502bcc80-0635-4225-bb72-546bdab002a1</t>
-  </si>
-  <si>
-    <t>Shoe Sorter</t>
-  </si>
-  <si>
-    <t>G17</t>
-  </si>
-  <si>
-    <t>ROW-153</t>
-  </si>
-  <si>
-    <t>b5e9b980-d725-44f1-99db-11edcbb0c9a5</t>
-  </si>
-  <si>
-    <t>ROW-154</t>
-  </si>
-  <si>
-    <t>d8c19d1a-cae8-4ce3-b2eb-8443e66b24be</t>
-  </si>
-  <si>
-    <t>Line 1</t>
-  </si>
-  <si>
-    <t>ROW-155</t>
-  </si>
-  <si>
-    <t>1a8d7dbf-a890-4fc7-80a8-6eecbd8efeab</t>
-  </si>
-  <si>
-    <t>Line 2</t>
-  </si>
-  <si>
-    <t>ROW-156</t>
-  </si>
-  <si>
-    <t>9744cbf8-ea82-4498-80f0-f898656ce9d0</t>
-  </si>
-  <si>
-    <t>Line 3</t>
-  </si>
-  <si>
-    <t>ROW-157</t>
-  </si>
-  <si>
-    <t>e3c14d73-c874-4306-8f66-5bfc05b346a4</t>
-  </si>
-  <si>
-    <t>Shoe sorter platform, near curtains</t>
-  </si>
-  <si>
-    <t>ROW-158</t>
-  </si>
-  <si>
-    <t>Pole on steps, 9 steps</t>
-  </si>
-  <si>
-    <t>8663694f-e644-4f38-965c-3be850570cde</t>
-  </si>
-  <si>
-    <t>Platform: Green mile/UIS</t>
-  </si>
-  <si>
-    <t>ROW-159</t>
-  </si>
-  <si>
-    <t>ee79f36b-bfb9-4cb7-84c0-c4e928bc4645</t>
-  </si>
-  <si>
-    <t>Platform: Far right on guard rail</t>
-  </si>
-  <si>
-    <t>ROW-160</t>
-  </si>
-  <si>
-    <t>c46c9e87-b3a4-4d14-897b-8ddb495a1e35</t>
-  </si>
-  <si>
-    <t>Platform: Jackpot</t>
-  </si>
-  <si>
-    <t>ROW-161</t>
-  </si>
-  <si>
-    <t>a3c7f1ad-5631-47d4-aa71-f6d713879668</t>
-  </si>
-  <si>
-    <t>Platform: Cross belt</t>
-  </si>
-  <si>
-    <t>ROW-162</t>
-  </si>
-  <si>
-    <t>6e8884a2-6812-4b05-afce-bbc7087cee64</t>
-  </si>
-  <si>
-    <t>Platform: near jackpot stairs</t>
-  </si>
-  <si>
-    <t>ROW-163</t>
-  </si>
-  <si>
-    <t>07609240-4231-44e1-88b7-64f40d47ad52</t>
-  </si>
-  <si>
-    <t>ROW-164</t>
-  </si>
-  <si>
-    <t>c68ce007-8106-42b0-b92c-40236d709ae4</t>
-  </si>
-  <si>
-    <t>Platform: near first line</t>
-  </si>
-  <si>
-    <t>ROW-165</t>
-  </si>
-  <si>
-    <t>aee43d33-d5a5-4488-8820-f863f86593c3</t>
-  </si>
-  <si>
-    <t>Platform: middle lane</t>
-  </si>
-  <si>
-    <t>ROW-166</t>
-  </si>
-  <si>
-    <t>Pole is in the chute RME uses to climb</t>
-  </si>
-  <si>
-    <t>e5dbf32e-fa4a-4d88-992c-fa74e4282477</t>
-  </si>
-  <si>
-    <t>H.2 3.3</t>
-  </si>
-  <si>
-    <t>PL 29</t>
-  </si>
-  <si>
-    <t>d1cde692-c933-4ee9-92ff-e7023a0483e8</t>
-  </si>
-  <si>
-    <t>H.5 4</t>
-  </si>
-  <si>
-    <t>ROW-168</t>
-  </si>
-  <si>
-    <t>f9ff4b0f-ffb8-4f4d-bcf4-2af2e82eec27</t>
-  </si>
-  <si>
-    <t>SR Ops Sign</t>
-  </si>
-  <si>
-    <t>ROW-169</t>
-  </si>
-  <si>
-    <t>bab717af-d62c-49e5-81e9-993feef17a97</t>
-  </si>
-  <si>
-    <t>H.5 5.2</t>
-  </si>
-  <si>
-    <t>ROW-170</t>
-  </si>
-  <si>
-    <t>09e1b4e2-5970-46e9-88aa-83d0233a3329</t>
-  </si>
-  <si>
-    <t>H.2 5.2</t>
-  </si>
-  <si>
-    <t>ROW-171</t>
-  </si>
-  <si>
-    <t>e2eb7157-dc1b-48db-8764-e848fae9c164</t>
-  </si>
-  <si>
-    <t>F. 8 5.2</t>
-  </si>
-  <si>
-    <t>ROW-172</t>
-  </si>
-  <si>
-    <t>92a642d8-5907-4776-a24b-3bb637c67e00</t>
-  </si>
-  <si>
-    <t>PID Injection 3</t>
-  </si>
-  <si>
-    <t>PL 31</t>
-  </si>
-  <si>
-    <t>8c6b5c71-e543-468a-9619-67f4d57e9578</t>
-  </si>
-  <si>
-    <t>E 7.5 5.2</t>
-  </si>
-  <si>
-    <t>ROW-174</t>
-  </si>
-  <si>
-    <t>4e495a04-5f1a-4eaf-9117-03607588d2f0</t>
-  </si>
-  <si>
-    <t>DD 213</t>
-  </si>
-  <si>
-    <t>PL 47</t>
-  </si>
-  <si>
-    <t>4e4b92b6-981f-4c6e-abd7-4cb7a10a3596</t>
-  </si>
-  <si>
-    <t>D6, see problem solve sign</t>
-  </si>
-  <si>
-    <t>ROW-176</t>
-  </si>
-  <si>
-    <t>2ed436fe-54c3-42c2-9ea4-271ee41f9e1f</t>
-  </si>
-  <si>
-    <t>Across MP 7</t>
-  </si>
-  <si>
-    <t>ROW-177</t>
-  </si>
-  <si>
-    <t>7be46d58-0e95-46ff-8b2f-31e04e0f4a23</t>
-  </si>
-  <si>
-    <t>ROW-178</t>
-  </si>
-  <si>
-    <t>c9cf2d78-e93c-4381-a518-7d41ad6f577d</t>
-  </si>
-  <si>
-    <t>NPC, E6</t>
-  </si>
-  <si>
-    <t>ROW-179</t>
-  </si>
-  <si>
-    <t>6ae8387a-b423-44f9-ad25-5782b7a03fdb</t>
-  </si>
-  <si>
-    <t>NPC, Problem Solve</t>
-  </si>
-  <si>
-    <t>ROW-180</t>
-  </si>
-  <si>
-    <t>e906a108-7ef1-47ad-a078-62b4cf9329b9</t>
-  </si>
-  <si>
-    <t>ROW-181</t>
-  </si>
-  <si>
-    <t>c13cbcee-619f-4c00-b7d7-af842ec083c0</t>
-  </si>
-  <si>
-    <t>NPC, G6</t>
-  </si>
-  <si>
-    <t>ROW-182</t>
-  </si>
-  <si>
-    <t>40dba955-c4df-45ca-9c9e-24b7d1d9f8e4</t>
-  </si>
-  <si>
-    <t>Leadership RME</t>
-  </si>
-  <si>
-    <t>ROW-183</t>
-  </si>
-  <si>
-    <t>527724b7-9c25-44bc-a296-66364e5cf6be</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>ROW-184</t>
-  </si>
-  <si>
-    <t>02c9b6a8-9b15-4762-97ae-583c36368365</t>
-  </si>
-  <si>
-    <t>Line 5</t>
-  </si>
-  <si>
-    <t>ROW-185</t>
-  </si>
-  <si>
-    <t>09da8703-b62e-44d0-a2eb-092ab7175589</t>
-  </si>
-  <si>
-    <t>ROW-186</t>
-  </si>
-  <si>
-    <t>d4caef39-2c23-4aad-aeda-008a92cf5689</t>
-  </si>
-  <si>
-    <t>ROW-187</t>
-  </si>
-  <si>
-    <t>e9a71286-cf76-4af0-87a1-538043521a62</t>
-  </si>
-  <si>
-    <t>ROW-188</t>
-  </si>
-  <si>
-    <t>e7a896ca-cc9e-46a0-9704-4c7d90d3ea34</t>
-  </si>
-  <si>
-    <t>ROW-189</t>
-  </si>
-  <si>
-    <t>1eaa66ff-ccaf-45d3-84b6-011ab1f71ddd</t>
-  </si>
-  <si>
-    <t>ROW-190</t>
-  </si>
-  <si>
-    <t>f95fa744-b7a1-4d67-89e1-5ac62ad1c6e4</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>ROW-191</t>
-  </si>
-  <si>
-    <t>01b7366d-dc09-4f6e-b8ce-b410ac24bf57</t>
   </si>
 </sst>
 </file>
@@ -2168,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q191"/>
+  <dimension ref="A1:Q193"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2286,10 +2298,10 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>50</v>
+        <v>51.233279102478505</v>
       </c>
       <c r="Q2">
-        <v>50</v>
+        <v>76.47735389226071</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -2339,10 +2351,10 @@
         <v>31</v>
       </c>
       <c r="P3">
-        <v>50</v>
+        <v>55.50633798731436</v>
       </c>
       <c r="Q3">
-        <v>50</v>
+        <v>76.47735389226071</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2392,10 +2404,10 @@
         <v>35</v>
       </c>
       <c r="P4">
-        <v>50</v>
+        <v>54.9852332452612</v>
       </c>
       <c r="Q4">
-        <v>50</v>
+        <v>75.87715883985857</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2445,10 +2457,10 @@
         <v>38</v>
       </c>
       <c r="P5">
-        <v>50</v>
+        <v>54.88101229685057</v>
       </c>
       <c r="Q5">
-        <v>50</v>
+        <v>72.87618357784793</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2498,10 +2510,10 @@
         <v>41</v>
       </c>
       <c r="P6">
-        <v>50</v>
+        <v>58.63296643963327</v>
       </c>
       <c r="Q6">
-        <v>50</v>
+        <v>75.72711007675804</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2551,10 +2563,10 @@
         <v>43</v>
       </c>
       <c r="P7">
-        <v>50</v>
+        <v>59.466734026918324</v>
       </c>
       <c r="Q7">
-        <v>50</v>
+        <v>76.47735389226071</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2604,10 +2616,10 @@
         <v>46</v>
       </c>
       <c r="P8">
-        <v>50</v>
+        <v>59.57095497532895</v>
       </c>
       <c r="Q8">
-        <v>50</v>
+        <v>73.02623234094845</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2657,10 +2669,10 @@
         <v>49</v>
       </c>
       <c r="P9">
-        <v>50</v>
+        <v>72.91123637188966</v>
       </c>
       <c r="Q9">
-        <v>50</v>
+        <v>72.87618357784793</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2689,31 +2701,31 @@
         <v>23</v>
       </c>
       <c r="I10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
         <v>52</v>
       </c>
-      <c r="J10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" t="s">
-        <v>53</v>
-      </c>
       <c r="P10">
-        <v>50</v>
+        <v>70.09727076480263</v>
       </c>
       <c r="Q10">
-        <v>50</v>
+        <v>72.57608605164685</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2721,19 +2733,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
         <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2742,7 +2754,7 @@
         <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J11" t="s">
         <v>25</v>
@@ -2760,13 +2772,13 @@
         <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P11">
-        <v>50</v>
+        <v>71.97324783619398</v>
       </c>
       <c r="Q11">
-        <v>50</v>
+        <v>65.97394047522342</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2774,19 +2786,19 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2813,24 +2825,24 @@
         <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P12">
-        <v>50</v>
+        <v>63.531351014932916</v>
       </c>
       <c r="Q12">
-        <v>50</v>
+        <v>70.32535460513886</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -2839,7 +2851,7 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2866,24 +2878,24 @@
         <v>25</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P13">
-        <v>50</v>
+        <v>73.64078460104953</v>
       </c>
       <c r="Q13">
-        <v>50</v>
+        <v>38.21491930162485</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2892,7 +2904,7 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2919,24 +2931,24 @@
         <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P14">
-        <v>50</v>
+        <v>76.2463083113153</v>
       </c>
       <c r="Q14">
-        <v>50</v>
+        <v>41.2158945636355</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -2945,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2972,24 +2984,24 @@
         <v>25</v>
       </c>
       <c r="O15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P15">
-        <v>50</v>
+        <v>76.5589711565472</v>
       </c>
       <c r="Q15">
-        <v>50</v>
+        <v>44.06682106254563</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -2998,7 +3010,7 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3025,24 +3037,24 @@
         <v>25</v>
       </c>
       <c r="O16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P16">
-        <v>50</v>
+        <v>76.45475020813656</v>
       </c>
       <c r="Q16">
-        <v>50</v>
+        <v>46.617650035254684</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -3051,7 +3063,7 @@
         <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3078,24 +3090,24 @@
         <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P17">
-        <v>50</v>
+        <v>76.76741305336844</v>
       </c>
       <c r="Q17">
-        <v>50</v>
+        <v>50.21882034966747</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -3104,7 +3116,7 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3131,24 +3143,24 @@
         <v>25</v>
       </c>
       <c r="O18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P18">
-        <v>50</v>
+        <v>76.76741305336844</v>
       </c>
       <c r="Q18">
-        <v>50</v>
+        <v>52.31950303307493</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -3157,7 +3169,7 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -3166,7 +3178,7 @@
         <v>23</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
@@ -3184,33 +3196,33 @@
         <v>25</v>
       </c>
       <c r="O19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P19">
-        <v>50</v>
+        <v>76.5589711565472</v>
       </c>
       <c r="Q19">
-        <v>50</v>
+        <v>54.420185716482386</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
         <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>84</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -3237,21 +3249,21 @@
         <v>25</v>
       </c>
       <c r="O20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P20">
-        <v>50</v>
+        <v>93.13010195383745</v>
       </c>
       <c r="Q20">
-        <v>50</v>
+        <v>61.02233129290583</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -3263,7 +3275,7 @@
         <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3290,21 +3302,21 @@
         <v>25</v>
       </c>
       <c r="O21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P21">
-        <v>50</v>
+        <v>93.6512066958906</v>
       </c>
       <c r="Q21">
-        <v>50</v>
+        <v>61.92262387150902</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -3316,7 +3328,7 @@
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3343,33 +3355,33 @@
         <v>25</v>
       </c>
       <c r="O22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P22">
-        <v>50</v>
+        <v>85.20930987462953</v>
       </c>
       <c r="Q22">
-        <v>50</v>
+        <v>58.621551083297305</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
         <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>92</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3396,21 +3408,21 @@
         <v>25</v>
       </c>
       <c r="O23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P23">
-        <v>50</v>
+        <v>86.04307746191458</v>
       </c>
       <c r="Q23">
-        <v>50</v>
+        <v>58.47150232019677</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -3422,7 +3434,7 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3434,48 +3446,48 @@
         <v>30</v>
       </c>
       <c r="J24" t="s">
+        <v>95</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+      <c r="O24" t="s">
         <v>96</v>
       </c>
-      <c r="K24" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" t="s">
-        <v>25</v>
-      </c>
-      <c r="O24" t="s">
-        <v>97</v>
-      </c>
       <c r="P24">
-        <v>50</v>
+        <v>81.97846047389999</v>
       </c>
       <c r="Q24">
-        <v>50</v>
+        <v>58.321453557096234</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
         <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>99</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3502,33 +3514,33 @@
         <v>25</v>
       </c>
       <c r="O25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25">
-        <v>50</v>
+        <v>93.02588100542681</v>
       </c>
       <c r="Q25">
-        <v>50</v>
+        <v>59.0716973725989</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s">
         <v>101</v>
-      </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>102</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3543,33 +3555,33 @@
         <v>25</v>
       </c>
       <c r="K26" t="s">
+        <v>102</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" t="s">
+        <v>25</v>
+      </c>
+      <c r="O26" t="s">
         <v>103</v>
       </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" t="s">
-        <v>104</v>
-      </c>
       <c r="P26">
-        <v>50</v>
+        <v>93.6512066958906</v>
       </c>
       <c r="Q26">
-        <v>50</v>
+        <v>57.42116097849305</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -3581,7 +3593,7 @@
         <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3608,33 +3620,33 @@
         <v>25</v>
       </c>
       <c r="O27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P27">
-        <v>50</v>
+        <v>93.02588100542681</v>
       </c>
       <c r="Q27">
-        <v>50</v>
+        <v>56.67091716299038</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
         <v>107</v>
-      </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" t="s">
-        <v>108</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3661,21 +3673,21 @@
         <v>25</v>
       </c>
       <c r="O28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28">
-        <v>50</v>
+        <v>92.6089972117843</v>
       </c>
       <c r="Q28">
-        <v>50</v>
+        <v>55.17042953198506</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
@@ -3687,7 +3699,7 @@
         <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3702,33 +3714,33 @@
         <v>25</v>
       </c>
       <c r="K29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" t="s">
         <v>111</v>
       </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>112</v>
-      </c>
       <c r="P29">
-        <v>50</v>
+        <v>91.77522962449926</v>
       </c>
       <c r="Q29">
-        <v>50</v>
+        <v>55.020380768884515</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -3740,7 +3752,7 @@
         <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -3767,21 +3779,21 @@
         <v>25</v>
       </c>
       <c r="O30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P30">
-        <v>50</v>
+        <v>93.13010195383745</v>
       </c>
       <c r="Q30">
-        <v>50</v>
+        <v>54.57023447958292</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
@@ -3793,7 +3805,7 @@
         <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3802,7 +3814,7 @@
         <v>23</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J31" t="s">
         <v>25</v>
@@ -3820,33 +3832,33 @@
         <v>25</v>
       </c>
       <c r="O31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P31">
-        <v>50</v>
+        <v>87.8148335848953</v>
       </c>
       <c r="Q31">
-        <v>50</v>
+        <v>55.770624584387186</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
         <v>117</v>
-      </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>118</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3873,21 +3885,21 @@
         <v>25</v>
       </c>
       <c r="O32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32">
-        <v>50</v>
+        <v>91.87945057290989</v>
       </c>
       <c r="Q32">
-        <v>50</v>
+        <v>51.86935674377333</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
@@ -3899,13 +3911,13 @@
         <v>33</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I33" t="s">
         <v>30</v>
@@ -3914,33 +3926,33 @@
         <v>25</v>
       </c>
       <c r="K33" t="s">
+        <v>122</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>25</v>
+      </c>
+      <c r="O33" t="s">
         <v>123</v>
       </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>25</v>
-      </c>
-      <c r="O33" t="s">
-        <v>124</v>
-      </c>
       <c r="P33">
-        <v>50</v>
+        <v>88.23171737853781</v>
       </c>
       <c r="Q33">
-        <v>50</v>
+        <v>52.31950303307493</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
@@ -3952,7 +3964,7 @@
         <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -3979,21 +3991,21 @@
         <v>25</v>
       </c>
       <c r="O34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P34">
-        <v>50</v>
+        <v>94.06809048953312</v>
       </c>
       <c r="Q34">
-        <v>50</v>
+        <v>51.86935674377333</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
@@ -4005,7 +4017,7 @@
         <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4020,45 +4032,45 @@
         <v>25</v>
       </c>
       <c r="K35" t="s">
+        <v>127</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>25</v>
+      </c>
+      <c r="O35" t="s">
         <v>128</v>
       </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" t="s">
-        <v>25</v>
-      </c>
-      <c r="O35" t="s">
-        <v>129</v>
-      </c>
       <c r="P35">
-        <v>50</v>
+        <v>93.02588100542681</v>
       </c>
       <c r="Q35">
-        <v>50</v>
+        <v>51.86935674377333</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
         <v>130</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" t="s">
-        <v>131</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -4070,36 +4082,36 @@
         <v>30</v>
       </c>
       <c r="J36" t="s">
+        <v>131</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>25</v>
+      </c>
+      <c r="O36" t="s">
         <v>132</v>
       </c>
-      <c r="K36" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" t="s">
-        <v>133</v>
-      </c>
       <c r="P36">
-        <v>50</v>
+        <v>93.23432290224808</v>
       </c>
       <c r="Q36">
-        <v>50</v>
+        <v>49.76867406036587</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -4111,23 +4123,23 @@
         <v>33</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="s">
+        <v>121</v>
+      </c>
+      <c r="I37" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
         <v>122</v>
       </c>
-      <c r="I37" t="s">
-        <v>52</v>
-      </c>
-      <c r="J37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" t="s">
-        <v>123</v>
-      </c>
       <c r="L37" t="s">
         <v>25</v>
       </c>
@@ -4138,33 +4150,33 @@
         <v>25</v>
       </c>
       <c r="O37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P37">
-        <v>50</v>
+        <v>87.60639168807403</v>
       </c>
       <c r="Q37">
-        <v>50</v>
+        <v>50.66896663896907</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
         <v>136</v>
-      </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>137</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -4191,33 +4203,33 @@
         <v>25</v>
       </c>
       <c r="O38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P38">
-        <v>50</v>
+        <v>93.85964859271186</v>
       </c>
       <c r="Q38">
-        <v>50</v>
+        <v>47.21784508765681</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
         <v>139</v>
-      </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>140</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -4244,21 +4256,21 @@
         <v>25</v>
       </c>
       <c r="O39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P39">
-        <v>50</v>
+        <v>92.2963343665524</v>
       </c>
       <c r="Q39">
-        <v>50</v>
+        <v>45.86740621975201</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -4270,7 +4282,7 @@
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4297,21 +4309,21 @@
         <v>25</v>
       </c>
       <c r="O40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P40">
-        <v>50</v>
+        <v>93.02588100542681</v>
       </c>
       <c r="Q40">
-        <v>50</v>
+        <v>45.267211167349885</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
@@ -4323,7 +4335,7 @@
         <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4332,10 +4344,10 @@
         <v>23</v>
       </c>
       <c r="I41" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="J41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K41" t="s">
         <v>25</v>
@@ -4353,15 +4365,15 @@
         <v>145</v>
       </c>
       <c r="P41">
-        <v>50</v>
+        <v>87.60639168807403</v>
       </c>
       <c r="Q41">
-        <v>50</v>
+        <v>47.21784508765681</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
         <v>146</v>
@@ -4388,7 +4400,7 @@
         <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K42" t="s">
         <v>25</v>
@@ -4406,15 +4418,15 @@
         <v>148</v>
       </c>
       <c r="P42">
-        <v>50</v>
+        <v>93.44276479906935</v>
       </c>
       <c r="Q42">
-        <v>50</v>
+        <v>43.01647972084189</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
         <v>149</v>
@@ -4441,7 +4453,7 @@
         <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K43" t="s">
         <v>25</v>
@@ -4459,15 +4471,15 @@
         <v>151</v>
       </c>
       <c r="P43">
-        <v>50</v>
+        <v>91.67100867608862</v>
       </c>
       <c r="Q43">
-        <v>50</v>
+        <v>41.6660408529371</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
         <v>149</v>
@@ -4494,7 +4506,7 @@
         <v>24</v>
       </c>
       <c r="J44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K44" t="s">
         <v>25</v>
@@ -4512,15 +4524,15 @@
         <v>153</v>
       </c>
       <c r="P44">
-        <v>50</v>
+        <v>94.06809048953312</v>
       </c>
       <c r="Q44">
-        <v>50</v>
+        <v>41.06584580053497</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
         <v>149</v>
@@ -4541,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I45" t="s">
         <v>30</v>
@@ -4550,7 +4562,7 @@
         <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L45" t="s">
         <v>25</v>
@@ -4565,15 +4577,15 @@
         <v>155</v>
       </c>
       <c r="P45">
-        <v>50</v>
+        <v>88.02327548171655</v>
       </c>
       <c r="Q45">
-        <v>50</v>
+        <v>41.81608961603763</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
         <v>156</v>
@@ -4618,15 +4630,15 @@
         <v>158</v>
       </c>
       <c r="P46">
-        <v>50</v>
+        <v>94.38075333476502</v>
       </c>
       <c r="Q46">
-        <v>50</v>
+        <v>38.36496806472538</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
         <v>159</v>
@@ -4653,7 +4665,7 @@
         <v>30</v>
       </c>
       <c r="J47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K47" t="s">
         <v>25</v>
@@ -4671,15 +4683,15 @@
         <v>161</v>
       </c>
       <c r="P47">
-        <v>50</v>
+        <v>91.35834583085672</v>
       </c>
       <c r="Q47">
-        <v>50</v>
+        <v>36.71443167061952</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
         <v>156</v>
@@ -4700,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I48" t="s">
         <v>24</v>
       </c>
       <c r="J48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K48" t="s">
         <v>25</v>
@@ -4724,15 +4736,15 @@
         <v>163</v>
       </c>
       <c r="P48">
-        <v>50</v>
+        <v>87.60639168807403</v>
       </c>
       <c r="Q48">
-        <v>50</v>
+        <v>38.36496806472538</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
         <v>164</v>
@@ -4759,7 +4771,7 @@
         <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K49" t="s">
         <v>166</v>
@@ -4777,21 +4789,21 @@
         <v>167</v>
       </c>
       <c r="P49">
-        <v>50</v>
+        <v>92.19211341814177</v>
       </c>
       <c r="Q49">
-        <v>50</v>
+        <v>38.06487053852432</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
         <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
@@ -4806,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I50" t="s">
         <v>24</v>
@@ -4830,21 +4842,21 @@
         <v>170</v>
       </c>
       <c r="P50">
-        <v>50</v>
+        <v>75.9336454660834</v>
       </c>
       <c r="Q50">
-        <v>50</v>
+        <v>47.66799137695841</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
         <v>171</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
@@ -4883,21 +4895,21 @@
         <v>173</v>
       </c>
       <c r="P51">
-        <v>50</v>
+        <v>80.72780909297241</v>
       </c>
       <c r="Q51">
-        <v>50</v>
+        <v>37.31462672302165</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
         <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
@@ -4936,21 +4948,21 @@
         <v>176</v>
       </c>
       <c r="P52">
-        <v>50</v>
+        <v>79.58137707017</v>
       </c>
       <c r="Q52">
-        <v>50</v>
+        <v>40.91579703743444</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
         <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
@@ -4968,7 +4980,7 @@
         <v>23</v>
       </c>
       <c r="I53" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J53" t="s">
         <v>25</v>
@@ -4989,21 +5001,21 @@
         <v>179</v>
       </c>
       <c r="P53">
-        <v>50</v>
+        <v>79.78981896699126</v>
       </c>
       <c r="Q53">
-        <v>50</v>
+        <v>42.5663334315403</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
         <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
@@ -5021,7 +5033,7 @@
         <v>23</v>
       </c>
       <c r="I54" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J54" t="s">
         <v>25</v>
@@ -5042,21 +5054,21 @@
         <v>182</v>
       </c>
       <c r="P54">
-        <v>50</v>
+        <v>73.22389921712154</v>
       </c>
       <c r="Q54">
-        <v>50</v>
+        <v>41.966138379138165</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
         <v>183</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
@@ -5095,21 +5107,21 @@
         <v>185</v>
       </c>
       <c r="P55">
-        <v>50</v>
+        <v>76.24630672102984</v>
       </c>
       <c r="Q55">
-        <v>50</v>
+        <v>41.515992089836566</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
@@ -5127,7 +5139,7 @@
         <v>23</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J56" t="s">
         <v>25</v>
@@ -5148,21 +5160,21 @@
         <v>187</v>
       </c>
       <c r="P56">
-        <v>50</v>
+        <v>78.22650474083181</v>
       </c>
       <c r="Q56">
-        <v>50</v>
+        <v>46.167503745953084</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="s">
         <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
         <v>20</v>
@@ -5201,21 +5213,21 @@
         <v>190</v>
       </c>
       <c r="P57">
-        <v>50</v>
+        <v>80.31092370904443</v>
       </c>
       <c r="Q57">
-        <v>50</v>
+        <v>45.267211167349885</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
         <v>191</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
@@ -5254,21 +5266,21 @@
         <v>193</v>
       </c>
       <c r="P58">
-        <v>50</v>
+        <v>79.78981896699126</v>
       </c>
       <c r="Q58">
-        <v>50</v>
+        <v>47.21784508765681</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
         <v>194</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -5307,21 +5319,21 @@
         <v>196</v>
       </c>
       <c r="P59">
-        <v>50</v>
+        <v>73.64078301076407</v>
       </c>
       <c r="Q59">
-        <v>50</v>
+        <v>50.21882034966747</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>197</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
@@ -5360,21 +5372,21 @@
         <v>199</v>
       </c>
       <c r="P60">
-        <v>50</v>
+        <v>79.1644932765275</v>
       </c>
       <c r="Q60">
-        <v>50</v>
+        <v>51.11911292827066</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>200</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
@@ -5413,21 +5425,21 @@
         <v>202</v>
       </c>
       <c r="P61">
-        <v>50</v>
+        <v>78.64338853447434</v>
       </c>
       <c r="Q61">
-        <v>50</v>
+        <v>53.36984437477865</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" t="s">
         <v>203</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
@@ -5466,21 +5478,21 @@
         <v>205</v>
       </c>
       <c r="P62">
-        <v>50</v>
+        <v>79.1644932765275</v>
       </c>
       <c r="Q62">
-        <v>50</v>
+        <v>56.370819636789314</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
         <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
@@ -5519,21 +5531,21 @@
         <v>208</v>
       </c>
       <c r="P63">
-        <v>50</v>
+        <v>74.787213443281</v>
       </c>
       <c r="Q63">
-        <v>50</v>
+        <v>55.470527058186114</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
         <v>209</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
@@ -5548,10 +5560,10 @@
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I64" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J64" t="s">
         <v>25</v>
@@ -5572,21 +5584,21 @@
         <v>211</v>
       </c>
       <c r="P64">
-        <v>50</v>
+        <v>85.62619207798659</v>
       </c>
       <c r="Q64">
-        <v>50</v>
+        <v>74.07657368265218</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
         <v>212</v>
       </c>
       <c r="C65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
@@ -5604,7 +5616,7 @@
         <v>23</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J65" t="s">
         <v>25</v>
@@ -5625,21 +5637,21 @@
         <v>214</v>
       </c>
       <c r="P65">
-        <v>50</v>
+        <v>83.12488931613144</v>
       </c>
       <c r="Q65">
-        <v>50</v>
+        <v>73.62642739335058</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
         <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
@@ -5678,21 +5690,21 @@
         <v>217</v>
       </c>
       <c r="P66">
-        <v>50</v>
+        <v>81.04047034791884</v>
       </c>
       <c r="Q66">
-        <v>50</v>
+        <v>73.92652491955165</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
         <v>218</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
@@ -5707,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I67" t="s">
         <v>30</v>
@@ -5731,21 +5743,21 @@
         <v>220</v>
       </c>
       <c r="P67">
-        <v>50</v>
+        <v>78.95605137970622</v>
       </c>
       <c r="Q67">
-        <v>50</v>
+        <v>73.77647615645111</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B68" t="s">
         <v>221</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -5760,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I68" t="s">
         <v>30</v>
@@ -5784,21 +5796,21 @@
         <v>223</v>
       </c>
       <c r="P68">
-        <v>50</v>
+        <v>85.20930828434405</v>
       </c>
       <c r="Q68">
-        <v>50</v>
+        <v>19.158726387857186</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" t="s">
         <v>224</v>
       </c>
       <c r="C69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -5837,21 +5849,21 @@
         <v>226</v>
       </c>
       <c r="P69">
-        <v>50</v>
+        <v>80.41514465745504</v>
       </c>
       <c r="Q69">
-        <v>50</v>
+        <v>55.470527058186114</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B70" t="s">
         <v>227</v>
       </c>
       <c r="C70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -5869,7 +5881,7 @@
         <v>23</v>
       </c>
       <c r="I70" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J70" t="s">
         <v>25</v>
@@ -5890,21 +5902,21 @@
         <v>229</v>
       </c>
       <c r="P70">
-        <v>50</v>
+        <v>80.10248181222316</v>
       </c>
       <c r="Q70">
-        <v>50</v>
+        <v>53.069746848577594</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" t="s">
         <v>230</v>
       </c>
       <c r="C71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
@@ -5919,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I71" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J71" t="s">
         <v>25</v>
@@ -5943,15 +5955,15 @@
         <v>232</v>
       </c>
       <c r="P71">
-        <v>50</v>
+        <v>80.72780750268694</v>
       </c>
       <c r="Q71">
-        <v>50</v>
+        <v>50.66896663896907</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B72" t="s">
         <v>233</v>
@@ -5996,15 +6008,15 @@
         <v>235</v>
       </c>
       <c r="P72">
-        <v>50</v>
+        <v>79.06027232811685</v>
       </c>
       <c r="Q72">
-        <v>50</v>
+        <v>49.16847900796374</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B73" t="s">
         <v>236</v>
@@ -6049,10 +6061,10 @@
         <v>238</v>
       </c>
       <c r="P73">
-        <v>50</v>
+        <v>71.796875</v>
       </c>
       <c r="Q73">
-        <v>50</v>
+        <v>35.12981558469393</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -6078,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I74" t="s">
         <v>30</v>
@@ -6102,10 +6114,10 @@
         <v>242</v>
       </c>
       <c r="P74">
-        <v>50</v>
+        <v>9.128015944583767</v>
       </c>
       <c r="Q74">
-        <v>50</v>
+        <v>76.47735389226071</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -6131,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I75" t="s">
         <v>30</v>
@@ -6155,10 +6167,10 @@
         <v>244</v>
       </c>
       <c r="P75">
-        <v>50</v>
+        <v>10.066004480279442</v>
       </c>
       <c r="Q75">
-        <v>50</v>
+        <v>76.77745141846177</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -6187,7 +6199,7 @@
         <v>23</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J76" t="s">
         <v>25</v>
@@ -6208,10 +6220,10 @@
         <v>247</v>
       </c>
       <c r="P76">
-        <v>50</v>
+        <v>11.6293187064389</v>
       </c>
       <c r="Q76">
-        <v>50</v>
+        <v>76.17725636605964</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -6237,10 +6249,10 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I77" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J77" t="s">
         <v>25</v>
@@ -6261,10 +6273,10 @@
         <v>249</v>
       </c>
       <c r="P77">
-        <v>50</v>
+        <v>12.254644396902684</v>
       </c>
       <c r="Q77">
-        <v>50</v>
+        <v>76.32730512916017</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -6314,10 +6326,10 @@
         <v>252</v>
       </c>
       <c r="P78">
-        <v>50</v>
+        <v>16.944587075381058</v>
       </c>
       <c r="Q78">
-        <v>50</v>
+        <v>75.87715883985857</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -6367,10 +6379,10 @@
         <v>255</v>
       </c>
       <c r="P79">
-        <v>50</v>
+        <v>18.299459404719254</v>
       </c>
       <c r="Q79">
-        <v>50</v>
+        <v>76.77745141846177</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -6420,10 +6432,10 @@
         <v>258</v>
       </c>
       <c r="P80">
-        <v>50</v>
+        <v>20.90498311498502</v>
       </c>
       <c r="Q80">
-        <v>50</v>
+        <v>77.07754894466284</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -6452,7 +6464,7 @@
         <v>23</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J81" t="s">
         <v>25</v>
@@ -6473,10 +6485,10 @@
         <v>261</v>
       </c>
       <c r="P81">
-        <v>50</v>
+        <v>22.885181134786997</v>
       </c>
       <c r="Q81">
-        <v>50</v>
+        <v>77.37764647086391</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -6526,10 +6538,10 @@
         <v>263</v>
       </c>
       <c r="P82">
-        <v>50</v>
+        <v>23.09362303160826</v>
       </c>
       <c r="Q82">
-        <v>50</v>
+        <v>73.47637863025005</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -6579,10 +6591,10 @@
         <v>266</v>
       </c>
       <c r="P83">
-        <v>50</v>
+        <v>28.200449503729157</v>
       </c>
       <c r="Q83">
-        <v>50</v>
+        <v>73.17628110404898</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -6632,10 +6644,10 @@
         <v>268</v>
       </c>
       <c r="P84">
-        <v>50</v>
+        <v>27.366681916444115</v>
       </c>
       <c r="Q84">
-        <v>50</v>
+        <v>74.07657368265218</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -6685,10 +6697,10 @@
         <v>271</v>
       </c>
       <c r="P85">
-        <v>50</v>
+        <v>29.13843803942483</v>
       </c>
       <c r="Q85">
-        <v>50</v>
+        <v>74.37667120885324</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -6714,7 +6726,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I86" t="s">
         <v>24</v>
@@ -6738,10 +6750,10 @@
         <v>274</v>
       </c>
       <c r="P86">
-        <v>50</v>
+        <v>32.05662459492248</v>
       </c>
       <c r="Q86">
-        <v>50</v>
+        <v>73.62642739335058</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -6791,10 +6803,10 @@
         <v>277</v>
       </c>
       <c r="P87">
-        <v>50</v>
+        <v>33.41149692426068</v>
       </c>
       <c r="Q87">
-        <v>50</v>
+        <v>74.07657368265218</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -6844,10 +6856,10 @@
         <v>280</v>
       </c>
       <c r="P88">
-        <v>50</v>
+        <v>35.28747399565203</v>
       </c>
       <c r="Q88">
-        <v>50</v>
+        <v>73.62642739335058</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -7088,7 +7100,7 @@
         <v>23</v>
       </c>
       <c r="I93" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J93" t="s">
         <v>25</v>
@@ -7141,10 +7153,10 @@
         <v>23</v>
       </c>
       <c r="I94" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K94" t="s">
         <v>25</v>
@@ -7197,7 +7209,7 @@
         <v>30</v>
       </c>
       <c r="J95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K95" t="s">
         <v>25</v>
@@ -7250,7 +7262,7 @@
         <v>30</v>
       </c>
       <c r="J96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K96" t="s">
         <v>25</v>
@@ -7297,13 +7309,13 @@
         <v>0</v>
       </c>
       <c r="H97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I97" t="s">
         <v>24</v>
       </c>
       <c r="J97" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K97" t="s">
         <v>25</v>
@@ -7356,7 +7368,7 @@
         <v>24</v>
       </c>
       <c r="J98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K98" t="s">
         <v>311</v>
@@ -7409,7 +7421,7 @@
         <v>30</v>
       </c>
       <c r="J99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K99" t="s">
         <v>25</v>
@@ -7456,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="H100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I100" t="s">
         <v>24</v>
@@ -7671,7 +7683,7 @@
         <v>23</v>
       </c>
       <c r="I104" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J104" t="s">
         <v>25</v>
@@ -7986,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I110" t="s">
         <v>24</v>
@@ -8434,10 +8446,10 @@
         <v>373</v>
       </c>
       <c r="P118">
-        <v>38.5625</v>
+        <v>37.5</v>
       </c>
       <c r="Q118">
-        <v>46.116585581192986</v>
+        <v>59.61368400159971</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -8540,10 +8552,10 @@
         <v>378</v>
       </c>
       <c r="P120">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="Q120">
-        <v>67.08207846089142</v>
+        <v>53.39152217899055</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -8572,7 +8584,7 @@
         <v>23</v>
       </c>
       <c r="I121" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J121" t="s">
         <v>25</v>
@@ -8805,10 +8817,10 @@
         <v>392</v>
       </c>
       <c r="P125">
-        <v>19.5625</v>
+        <v>19.21875</v>
       </c>
       <c r="Q125">
-        <v>63.278896427673494</v>
+        <v>50.287747939793256</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -8858,10 +8870,10 @@
         <v>394</v>
       </c>
       <c r="P126">
-        <v>21.25</v>
+        <v>19.21875</v>
       </c>
       <c r="Q126">
-        <v>63.04995915009404</v>
+        <v>50.287747939793256</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -8887,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I127" t="s">
         <v>24</v>
@@ -8964,10 +8976,10 @@
         <v>399</v>
       </c>
       <c r="P128">
-        <v>21.484375</v>
+        <v>19.21875</v>
       </c>
       <c r="Q128">
-        <v>66.2161426498899</v>
+        <v>50.287747939793256</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -9017,10 +9029,10 @@
         <v>401</v>
       </c>
       <c r="P129">
-        <v>21.796875</v>
+        <v>19.21875</v>
       </c>
       <c r="Q129">
-        <v>52.31230497526489</v>
+        <v>50.287747939793256</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -9123,10 +9135,10 @@
         <v>406</v>
       </c>
       <c r="P131">
-        <v>18.515625</v>
+        <v>18.75</v>
       </c>
       <c r="Q131">
-        <v>35.21604556461562</v>
+        <v>37.24060260008724</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -9229,10 +9241,10 @@
         <v>412</v>
       </c>
       <c r="P133">
-        <v>50</v>
+        <v>49.461522979497786</v>
       </c>
       <c r="Q133">
-        <v>50</v>
+        <v>23.510140517772637</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -9282,10 +9294,10 @@
         <v>415</v>
       </c>
       <c r="P134">
-        <v>50</v>
+        <v>47.793987804927696</v>
       </c>
       <c r="Q134">
-        <v>50</v>
+        <v>24.11033557017477</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -9335,10 +9347,10 @@
         <v>418</v>
       </c>
       <c r="P135">
-        <v>50</v>
+        <v>54.35990755479742</v>
       </c>
       <c r="Q135">
-        <v>50</v>
+        <v>24.860579385677433</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -9388,10 +9400,10 @@
         <v>421</v>
       </c>
       <c r="P136">
-        <v>50</v>
+        <v>45.60534788830445</v>
       </c>
       <c r="Q136">
-        <v>50</v>
+        <v>15.857653599645467</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -9420,7 +9432,7 @@
         <v>23</v>
       </c>
       <c r="I137" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J137" t="s">
         <v>25</v>
@@ -9441,10 +9453,10 @@
         <v>424</v>
       </c>
       <c r="P137">
-        <v>50</v>
+        <v>57.395833333333336</v>
       </c>
       <c r="Q137">
-        <v>50</v>
+        <v>24.944387358898627</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -9473,7 +9485,7 @@
         <v>23</v>
       </c>
       <c r="I138" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
@@ -9526,7 +9538,7 @@
         <v>23</v>
       </c>
       <c r="I139" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J139" t="s">
         <v>25</v>
@@ -9547,10 +9559,10 @@
         <v>429</v>
       </c>
       <c r="P139">
-        <v>50</v>
+        <v>42.79138228121743</v>
       </c>
       <c r="Q139">
-        <v>50</v>
+        <v>17.65823875685186</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -9600,10 +9612,10 @@
         <v>432</v>
       </c>
       <c r="P140">
-        <v>50</v>
+        <v>43.93781271373437</v>
       </c>
       <c r="Q140">
-        <v>50</v>
+        <v>15.107409784142803</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -9635,7 +9647,7 @@
         <v>30</v>
       </c>
       <c r="J141" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K141" t="s">
         <v>436</v>
@@ -9653,10 +9665,10 @@
         <v>437</v>
       </c>
       <c r="P141">
-        <v>60.62499999999999</v>
+        <v>60</v>
       </c>
       <c r="Q141">
-        <v>35.93213986573936</v>
+        <v>37.619270844453126</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -9706,10 +9718,10 @@
         <v>441</v>
       </c>
       <c r="P142">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q142">
-        <v>50</v>
+        <v>37.619270844453126</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -9735,7 +9747,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I143" t="s">
         <v>24</v>
@@ -9971,10 +9983,10 @@
         <v>461</v>
       </c>
       <c r="P147">
-        <v>50</v>
+        <v>44.45891745578752</v>
       </c>
       <c r="Q147">
-        <v>50</v>
+        <v>18.858628861656122</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -10024,10 +10036,10 @@
         <v>465</v>
       </c>
       <c r="P148">
-        <v>50</v>
+        <v>27.421875</v>
       </c>
       <c r="Q148">
-        <v>50</v>
+        <v>36.66697993737927</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -10077,10 +10089,10 @@
         <v>468</v>
       </c>
       <c r="P149">
-        <v>47.604166666666664</v>
+        <v>27.421875</v>
       </c>
       <c r="Q149">
-        <v>36.07188577447725</v>
+        <v>36.66697993737927</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -10130,10 +10142,10 @@
         <v>471</v>
       </c>
       <c r="P150">
-        <v>50</v>
+        <v>27.421875</v>
       </c>
       <c r="Q150">
-        <v>50</v>
+        <v>36.66697993737927</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -10236,10 +10248,10 @@
         <v>477</v>
       </c>
       <c r="P152">
-        <v>50</v>
+        <v>56.32812499999999</v>
       </c>
       <c r="Q152">
-        <v>50</v>
+        <v>34.90486478753209</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -10250,7 +10262,7 @@
         <v>479</v>
       </c>
       <c r="C153" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D153" t="s">
         <v>20</v>
@@ -10268,7 +10280,7 @@
         <v>23</v>
       </c>
       <c r="I153" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="J153" t="s">
         <v>464</v>
@@ -10289,10 +10301,10 @@
         <v>481</v>
       </c>
       <c r="P153">
-        <v>50</v>
+        <v>9.753341635047551</v>
       </c>
       <c r="Q153">
-        <v>50</v>
+        <v>60.4221362405037</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -10303,7 +10315,7 @@
         <v>168</v>
       </c>
       <c r="C154" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D154" t="s">
         <v>20</v>
@@ -10342,10 +10354,10 @@
         <v>483</v>
       </c>
       <c r="P154">
-        <v>50</v>
+        <v>6.6267131827286345</v>
       </c>
       <c r="Q154">
-        <v>50</v>
+        <v>57.721258504694106</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -10356,7 +10368,7 @@
         <v>484</v>
       </c>
       <c r="C155" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D155" t="s">
         <v>20</v>
@@ -10395,10 +10407,10 @@
         <v>486</v>
       </c>
       <c r="P155">
-        <v>50</v>
+        <v>7.043596976371156</v>
       </c>
       <c r="Q155">
-        <v>50</v>
+        <v>49.16847900796374</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -10409,7 +10421,7 @@
         <v>487</v>
       </c>
       <c r="C156" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D156" t="s">
         <v>20</v>
@@ -10448,10 +10460,10 @@
         <v>489</v>
       </c>
       <c r="P156">
-        <v>50</v>
+        <v>6.835155079549896</v>
       </c>
       <c r="Q156">
-        <v>50</v>
+        <v>59.9719899512021</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -10462,7 +10474,7 @@
         <v>490</v>
       </c>
       <c r="C157" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
@@ -10501,10 +10513,10 @@
         <v>492</v>
       </c>
       <c r="P157">
-        <v>50</v>
+        <v>10.482888273921965</v>
       </c>
       <c r="Q157">
-        <v>50</v>
+        <v>64.32340408111756</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -10515,7 +10527,7 @@
         <v>493</v>
       </c>
       <c r="C158" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D158" t="s">
         <v>32</v>
@@ -10530,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="H158" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I158" t="s">
         <v>30</v>
@@ -10554,10 +10566,10 @@
         <v>496</v>
       </c>
       <c r="P158">
-        <v>50</v>
+        <v>6.209829389086113</v>
       </c>
       <c r="Q158">
-        <v>50</v>
+        <v>67.7745256324298</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -10568,7 +10580,7 @@
         <v>497</v>
       </c>
       <c r="C159" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D159" t="s">
         <v>20</v>
@@ -10607,10 +10619,10 @@
         <v>499</v>
       </c>
       <c r="P159">
-        <v>50</v>
+        <v>4.2296313692841325</v>
       </c>
       <c r="Q159">
-        <v>50</v>
+        <v>42.26623590533924</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -10621,7 +10633,7 @@
         <v>500</v>
       </c>
       <c r="C160" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -10660,10 +10672,10 @@
         <v>502</v>
       </c>
       <c r="P160">
-        <v>50</v>
+        <v>10.170225428690074</v>
       </c>
       <c r="Q160">
-        <v>50</v>
+        <v>54.72028324268345</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -10674,7 +10686,7 @@
         <v>503</v>
       </c>
       <c r="C161" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
@@ -10689,7 +10701,7 @@
         <v>1</v>
       </c>
       <c r="H161" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I161" t="s">
         <v>30</v>
@@ -10713,10 +10725,10 @@
         <v>505</v>
       </c>
       <c r="P161">
-        <v>50</v>
+        <v>10.066004480279442</v>
       </c>
       <c r="Q161">
-        <v>50</v>
+        <v>58.621551083297305</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -10727,7 +10739,7 @@
         <v>506</v>
       </c>
       <c r="C162" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D162" t="s">
         <v>20</v>
@@ -10766,10 +10778,10 @@
         <v>508</v>
       </c>
       <c r="P162">
-        <v>50</v>
+        <v>7.66892266683494</v>
       </c>
       <c r="Q162">
-        <v>50</v>
+        <v>62.82291645011222</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -10780,7 +10792,7 @@
         <v>509</v>
       </c>
       <c r="C163" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -10795,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="H163" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I163" t="s">
         <v>30</v>
@@ -10819,10 +10831,10 @@
         <v>511</v>
       </c>
       <c r="P163">
-        <v>50</v>
+        <v>9.0625</v>
       </c>
       <c r="Q163">
-        <v>50</v>
+        <v>46.752271372692675</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -10833,7 +10845,7 @@
         <v>509</v>
       </c>
       <c r="C164" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -10886,7 +10898,7 @@
         <v>514</v>
       </c>
       <c r="C165" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -10925,10 +10937,10 @@
         <v>516</v>
       </c>
       <c r="P165">
-        <v>50</v>
+        <v>7.147817924781788</v>
       </c>
       <c r="Q165">
-        <v>50</v>
+        <v>54.870332005783986</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -10939,7 +10951,7 @@
         <v>517</v>
       </c>
       <c r="C166" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -10954,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="H166" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I166" t="s">
         <v>24</v>
@@ -10978,15 +10990,15 @@
         <v>520</v>
       </c>
       <c r="P166">
-        <v>50</v>
+        <v>8.919574047762506</v>
       </c>
       <c r="Q166">
-        <v>50</v>
+        <v>51.86935674377333</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B167" t="s">
         <v>521</v>
@@ -11031,15 +11043,15 @@
         <v>523</v>
       </c>
       <c r="P167">
-        <v>50</v>
+        <v>82.65625</v>
       </c>
       <c r="Q167">
-        <v>50</v>
+        <v>40.41615931799708</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B168" t="s">
         <v>524</v>
@@ -11084,15 +11096,15 @@
         <v>526</v>
       </c>
       <c r="P168">
-        <v>50</v>
+        <v>83.125</v>
       </c>
       <c r="Q168">
-        <v>50</v>
+        <v>41.2034871080635</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B169" t="s">
         <v>527</v>
@@ -11137,15 +11149,15 @@
         <v>529</v>
       </c>
       <c r="P169">
-        <v>50</v>
+        <v>78.43494822793853</v>
       </c>
       <c r="Q169">
-        <v>50</v>
+        <v>30.962563181619906</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B170" t="s">
         <v>530</v>
@@ -11190,15 +11202,15 @@
         <v>532</v>
       </c>
       <c r="P170">
-        <v>50</v>
+        <v>81.40625</v>
       </c>
       <c r="Q170">
-        <v>50</v>
+        <v>41.46592800229455</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B171" t="s">
         <v>533</v>
@@ -11243,15 +11255,15 @@
         <v>535</v>
       </c>
       <c r="P171">
-        <v>50</v>
+        <v>82.734375</v>
       </c>
       <c r="Q171">
-        <v>50</v>
+        <v>46.03992924704297</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B172" t="s">
         <v>536</v>
@@ -11296,15 +11308,15 @@
         <v>538</v>
       </c>
       <c r="P172">
-        <v>50</v>
+        <v>82.8125</v>
       </c>
       <c r="Q172">
-        <v>50</v>
+        <v>39.17892993360697</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B173" t="s">
         <v>539</v>
@@ -11325,7 +11337,7 @@
         <v>0</v>
       </c>
       <c r="H173" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I173" t="s">
         <v>24</v>
@@ -11349,15 +11361,15 @@
         <v>541</v>
       </c>
       <c r="P173">
-        <v>50</v>
+        <v>81.66579603838262</v>
       </c>
       <c r="Q173">
-        <v>50</v>
+        <v>46.71768330717585</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B174" t="s">
         <v>542</v>
@@ -11402,15 +11414,15 @@
         <v>544</v>
       </c>
       <c r="P174">
-        <v>50</v>
+        <v>82.734375</v>
       </c>
       <c r="Q174">
-        <v>50</v>
+        <v>44.01537207258645</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B175" t="s">
         <v>545</v>
@@ -11455,15 +11467,15 @@
         <v>547</v>
       </c>
       <c r="P175">
-        <v>50</v>
+        <v>93.23432290224808</v>
       </c>
       <c r="Q175">
-        <v>50</v>
+        <v>57.57120974159358</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B176" t="s">
         <v>548</v>
@@ -11508,10 +11520,10 @@
         <v>550</v>
       </c>
       <c r="P176">
-        <v>50</v>
+        <v>69.57616602274948</v>
       </c>
       <c r="Q176">
-        <v>50</v>
+        <v>62.47280343273178</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -11561,10 +11573,10 @@
         <v>553</v>
       </c>
       <c r="P177">
-        <v>50</v>
+        <v>68.42973559023254</v>
       </c>
       <c r="Q177">
-        <v>50</v>
+        <v>66.52412003644616</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -11614,15 +11626,15 @@
         <v>555</v>
       </c>
       <c r="P178">
-        <v>50</v>
+        <v>71.55636404255145</v>
       </c>
       <c r="Q178">
-        <v>50</v>
+        <v>66.37407127334563</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B179" t="s">
         <v>556</v>
@@ -11643,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I179" t="s">
         <v>30</v>
@@ -11667,15 +11679,15 @@
         <v>558</v>
       </c>
       <c r="P179">
-        <v>50</v>
+        <v>69.36772412592822</v>
       </c>
       <c r="Q179">
-        <v>50</v>
+        <v>53.319828883599286</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B180" t="s">
         <v>559</v>
@@ -11696,7 +11708,7 @@
         <v>1</v>
       </c>
       <c r="H180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I180" t="s">
         <v>30</v>
@@ -11720,15 +11732,15 @@
         <v>561</v>
       </c>
       <c r="P180">
-        <v>50</v>
+        <v>70.93103835208767</v>
       </c>
       <c r="Q180">
-        <v>50</v>
+        <v>56.32080414560994</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B181" t="s">
         <v>559</v>
@@ -11749,7 +11761,7 @@
         <v>1</v>
       </c>
       <c r="H181" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I181" t="s">
         <v>30</v>
@@ -11773,15 +11785,15 @@
         <v>563</v>
       </c>
       <c r="P181">
-        <v>50</v>
+        <v>71.55636404255145</v>
       </c>
       <c r="Q181">
-        <v>50</v>
+        <v>58.72158435521847</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B182" t="s">
         <v>564</v>
@@ -11826,15 +11838,15 @@
         <v>566</v>
       </c>
       <c r="P182">
-        <v>50</v>
+        <v>70.40993361003453</v>
       </c>
       <c r="Q182">
-        <v>50</v>
+        <v>45.66734196547212</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B183" t="s">
         <v>567</v>
@@ -11879,10 +11891,10 @@
         <v>569</v>
       </c>
       <c r="P183">
-        <v>50</v>
+        <v>70.61837550685578</v>
       </c>
       <c r="Q183">
-        <v>50</v>
+        <v>37.86480628424441</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -11932,10 +11944,10 @@
         <v>572</v>
       </c>
       <c r="P184">
-        <v>50</v>
+        <v>58.111861697580125</v>
       </c>
       <c r="Q184">
-        <v>50</v>
+        <v>48.96841475368384</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -11985,10 +11997,10 @@
         <v>575</v>
       </c>
       <c r="P185">
-        <v>50</v>
+        <v>61.75959489195218</v>
       </c>
       <c r="Q185">
-        <v>50</v>
+        <v>39.81544020455134</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -12038,10 +12050,10 @@
         <v>577</v>
       </c>
       <c r="P186">
-        <v>50</v>
+        <v>60.82160635625652</v>
       </c>
       <c r="Q186">
-        <v>50</v>
+        <v>43.86675680826572</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -12091,10 +12103,10 @@
         <v>579</v>
       </c>
       <c r="P187">
-        <v>50</v>
+        <v>62.072257737184074</v>
       </c>
       <c r="Q187">
-        <v>50</v>
+        <v>47.167829596477446</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -12144,10 +12156,10 @@
         <v>581</v>
       </c>
       <c r="P188">
-        <v>50</v>
+        <v>61.551152995130934</v>
       </c>
       <c r="Q188">
-        <v>50</v>
+        <v>59.92197446002273</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -12197,10 +12209,10 @@
         <v>583</v>
       </c>
       <c r="P189">
-        <v>50</v>
+        <v>59.7793968721502</v>
       </c>
       <c r="Q189">
-        <v>50</v>
+        <v>56.47085290871048</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -12250,10 +12262,10 @@
         <v>585</v>
       </c>
       <c r="P190">
-        <v>50</v>
+        <v>61.96803678877345</v>
       </c>
       <c r="Q190">
-        <v>50</v>
+        <v>56.47085290871048</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -12303,15 +12315,121 @@
         <v>588</v>
       </c>
       <c r="P191">
-        <v>50</v>
+        <v>50.08684866996157</v>
       </c>
       <c r="Q191">
-        <v>50</v>
+        <v>56.77095043491154</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>433</v>
+      </c>
+      <c r="B192" t="s">
+        <v>25</v>
+      </c>
+      <c r="C192" t="s">
+        <v>589</v>
+      </c>
+      <c r="D192" t="s">
+        <v>25</v>
+      </c>
+      <c r="E192" t="s">
+        <v>21</v>
+      </c>
+      <c r="F192" t="s">
+        <v>480</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192" t="s">
+        <v>121</v>
+      </c>
+      <c r="I192" t="s">
+        <v>30</v>
+      </c>
+      <c r="J192" t="s">
+        <v>131</v>
+      </c>
+      <c r="K192" t="s">
+        <v>25</v>
+      </c>
+      <c r="L192" t="s">
+        <v>25</v>
+      </c>
+      <c r="M192" t="s">
+        <v>590</v>
+      </c>
+      <c r="N192" t="s">
+        <v>25</v>
+      </c>
+      <c r="O192" t="s">
+        <v>591</v>
+      </c>
+      <c r="P192">
+        <v>47.15625</v>
+      </c>
+      <c r="Q192">
+        <v>50.10666707356771</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>17</v>
+      </c>
+      <c r="B193" t="s">
+        <v>18</v>
+      </c>
+      <c r="C193" t="s">
+        <v>19</v>
+      </c>
+      <c r="D193" t="s">
+        <v>20</v>
+      </c>
+      <c r="E193" t="s">
+        <v>21</v>
+      </c>
+      <c r="F193" t="s">
+        <v>22</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" t="s">
+        <v>24</v>
+      </c>
+      <c r="J193" t="s">
+        <v>25</v>
+      </c>
+      <c r="K193" t="s">
+        <v>25</v>
+      </c>
+      <c r="L193" t="s">
+        <v>25</v>
+      </c>
+      <c r="M193" t="s">
+        <v>590</v>
+      </c>
+      <c r="N193" t="s">
+        <v>25</v>
+      </c>
+      <c r="O193" t="s">
+        <v>592</v>
+      </c>
+      <c r="P193">
+        <v>51.38092911280489</v>
+      </c>
+      <c r="Q193">
+        <v>72.38727831139086</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/data/equipment.xlsx
+++ b/data/equipment.xlsx
@@ -693,6 +693,9 @@
     <t>ROW-69</t>
   </si>
   <si>
+    <t>current-user</t>
+  </si>
+  <si>
     <t>58dd3900-a434-4f8a-892c-b6132c67e9c7</t>
   </si>
   <si>
@@ -1783,9 +1786,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>current-user</t>
   </si>
   <si>
     <t>93422e06-4964-4837-900b-dd417f1751fe</t>
@@ -5840,19 +5840,19 @@
         <v>25</v>
       </c>
       <c r="M69" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N69" t="s">
         <v>25</v>
       </c>
       <c r="O69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P69">
-        <v>80.41514465745504</v>
+        <v>83.4375</v>
       </c>
       <c r="Q69">
-        <v>55.470527058186114</v>
+        <v>20.860047227249183</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -5860,7 +5860,7 @@
         <v>59</v>
       </c>
       <c r="B70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C70" t="s">
         <v>61</v>
@@ -5872,7 +5872,7 @@
         <v>21</v>
       </c>
       <c r="F70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -5893,19 +5893,19 @@
         <v>25</v>
       </c>
       <c r="M70" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N70" t="s">
         <v>25</v>
       </c>
       <c r="O70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70">
-        <v>80.10248181222316</v>
+        <v>81.40625</v>
       </c>
       <c r="Q70">
-        <v>53.069746848577594</v>
+        <v>19.73531432042284</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C71" t="s">
         <v>61</v>
@@ -5925,7 +5925,7 @@
         <v>21</v>
       </c>
       <c r="F71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -5946,19 +5946,19 @@
         <v>25</v>
       </c>
       <c r="M71" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N71" t="s">
         <v>25</v>
       </c>
       <c r="O71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71">
-        <v>80.72780750268694</v>
+        <v>78.59375</v>
       </c>
       <c r="Q71">
-        <v>50.66896663896907</v>
+        <v>20.185207483153377</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -5978,7 +5978,7 @@
         <v>21</v>
       </c>
       <c r="F72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -6005,7 +6005,7 @@
         <v>25</v>
       </c>
       <c r="O72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P72">
         <v>79.06027232811685</v>
@@ -6019,7 +6019,7 @@
         <v>59</v>
       </c>
       <c r="B73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C73" t="s">
         <v>19</v>
@@ -6031,7 +6031,7 @@
         <v>21</v>
       </c>
       <c r="F73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>25</v>
       </c>
       <c r="O73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P73">
         <v>71.796875</v>
@@ -6069,10 +6069,10 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C74" t="s">
         <v>19</v>
@@ -6084,7 +6084,7 @@
         <v>21</v>
       </c>
       <c r="F74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6111,7 +6111,7 @@
         <v>25</v>
       </c>
       <c r="O74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74">
         <v>9.128015944583767</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C75" t="s">
         <v>19</v>
@@ -6137,7 +6137,7 @@
         <v>33</v>
       </c>
       <c r="F75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -6164,7 +6164,7 @@
         <v>25</v>
       </c>
       <c r="O75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P75">
         <v>10.066004480279442</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s">
         <v>19</v>
@@ -6190,7 +6190,7 @@
         <v>21</v>
       </c>
       <c r="F76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -6217,7 +6217,7 @@
         <v>25</v>
       </c>
       <c r="O76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76">
         <v>11.6293187064389</v>
@@ -6228,10 +6228,10 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C77" t="s">
         <v>19</v>
@@ -6243,7 +6243,7 @@
         <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6270,7 +6270,7 @@
         <v>25</v>
       </c>
       <c r="O77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77">
         <v>12.254644396902684</v>
@@ -6281,10 +6281,10 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C78" t="s">
         <v>19</v>
@@ -6296,7 +6296,7 @@
         <v>21</v>
       </c>
       <c r="F78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6323,7 +6323,7 @@
         <v>25</v>
       </c>
       <c r="O78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78">
         <v>16.944587075381058</v>
@@ -6334,10 +6334,10 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C79" t="s">
         <v>19</v>
@@ -6349,7 +6349,7 @@
         <v>33</v>
       </c>
       <c r="F79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         <v>25</v>
       </c>
       <c r="O79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P79">
         <v>18.299459404719254</v>
@@ -6387,10 +6387,10 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -6402,7 +6402,7 @@
         <v>21</v>
       </c>
       <c r="F80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -6429,7 +6429,7 @@
         <v>25</v>
       </c>
       <c r="O80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P80">
         <v>20.90498311498502</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C81" t="s">
         <v>19</v>
@@ -6455,7 +6455,7 @@
         <v>33</v>
       </c>
       <c r="F81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -6482,7 +6482,7 @@
         <v>25</v>
       </c>
       <c r="O81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P81">
         <v>22.885181134786997</v>
@@ -6493,10 +6493,10 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s">
         <v>19</v>
@@ -6508,7 +6508,7 @@
         <v>21</v>
       </c>
       <c r="F82" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -6535,7 +6535,7 @@
         <v>25</v>
       </c>
       <c r="O82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P82">
         <v>23.09362303160826</v>
@@ -6546,10 +6546,10 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C83" t="s">
         <v>19</v>
@@ -6561,7 +6561,7 @@
         <v>21</v>
       </c>
       <c r="F83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G83">
         <v>2</v>
@@ -6588,7 +6588,7 @@
         <v>25</v>
       </c>
       <c r="O83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P83">
         <v>28.200449503729157</v>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C84" t="s">
         <v>19</v>
@@ -6614,7 +6614,7 @@
         <v>33</v>
       </c>
       <c r="F84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>25</v>
       </c>
       <c r="O84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P84">
         <v>27.366681916444115</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s">
         <v>19</v>
@@ -6667,7 +6667,7 @@
         <v>33</v>
       </c>
       <c r="F85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -6694,7 +6694,7 @@
         <v>25</v>
       </c>
       <c r="O85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P85">
         <v>29.13843803942483</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C86" t="s">
         <v>19</v>
@@ -6720,7 +6720,7 @@
         <v>33</v>
       </c>
       <c r="F86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>25</v>
       </c>
       <c r="O86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P86">
         <v>32.05662459492248</v>
@@ -6758,10 +6758,10 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C87" t="s">
         <v>19</v>
@@ -6773,7 +6773,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G87">
         <v>2</v>
@@ -6800,7 +6800,7 @@
         <v>25</v>
       </c>
       <c r="O87" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P87">
         <v>33.41149692426068</v>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B88" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C88" t="s">
         <v>19</v>
@@ -6826,7 +6826,7 @@
         <v>33</v>
       </c>
       <c r="F88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -6853,7 +6853,7 @@
         <v>25</v>
       </c>
       <c r="O88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P88">
         <v>35.28747399565203</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C89" t="s">
         <v>19</v>
@@ -6879,7 +6879,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -6906,7 +6906,7 @@
         <v>25</v>
       </c>
       <c r="O89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P89">
         <v>6.5625</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C90" t="s">
         <v>19</v>
@@ -6932,7 +6932,7 @@
         <v>21</v>
       </c>
       <c r="F90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -6959,7 +6959,7 @@
         <v>25</v>
       </c>
       <c r="O90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P90">
         <v>8.229166666666666</v>
@@ -6970,10 +6970,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C91" t="s">
         <v>19</v>
@@ -6985,7 +6985,7 @@
         <v>21</v>
       </c>
       <c r="F91" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -7012,7 +7012,7 @@
         <v>25</v>
       </c>
       <c r="O91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P91">
         <v>44.6875</v>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B92" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
         <v>19</v>
@@ -7038,7 +7038,7 @@
         <v>21</v>
       </c>
       <c r="F92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -7065,7 +7065,7 @@
         <v>25</v>
       </c>
       <c r="O92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P92">
         <v>42.604166666666664</v>
@@ -7076,10 +7076,10 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
         <v>19</v>
@@ -7091,7 +7091,7 @@
         <v>33</v>
       </c>
       <c r="F93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -7118,7 +7118,7 @@
         <v>25</v>
       </c>
       <c r="O93" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P93">
         <v>37.916666666666664</v>
@@ -7129,10 +7129,10 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B94" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s">
         <v>19</v>
@@ -7144,7 +7144,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G94">
         <v>3</v>
@@ -7171,7 +7171,7 @@
         <v>25</v>
       </c>
       <c r="O94" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P94">
         <v>36.354166666666664</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C95" t="s">
         <v>19</v>
@@ -7197,7 +7197,7 @@
         <v>33</v>
       </c>
       <c r="F95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -7224,7 +7224,7 @@
         <v>25</v>
       </c>
       <c r="O95" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P95">
         <v>35.208333333333336</v>
@@ -7235,10 +7235,10 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C96" t="s">
         <v>19</v>
@@ -7250,7 +7250,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -7277,7 +7277,7 @@
         <v>25</v>
       </c>
       <c r="O96" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P96">
         <v>32.395833333333336</v>
@@ -7288,10 +7288,10 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C97" t="s">
         <v>19</v>
@@ -7303,7 +7303,7 @@
         <v>33</v>
       </c>
       <c r="F97" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -7330,7 +7330,7 @@
         <v>25</v>
       </c>
       <c r="O97" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P97">
         <v>32.1875</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s">
         <v>19</v>
@@ -7356,7 +7356,7 @@
         <v>33</v>
       </c>
       <c r="F98" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>131</v>
       </c>
       <c r="K98" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L98" t="s">
         <v>25</v>
@@ -7383,7 +7383,7 @@
         <v>25</v>
       </c>
       <c r="O98" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P98">
         <v>30.729166666666668</v>
@@ -7394,10 +7394,10 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
@@ -7409,7 +7409,7 @@
         <v>21</v>
       </c>
       <c r="F99" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -7436,7 +7436,7 @@
         <v>25</v>
       </c>
       <c r="O99" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P99">
         <v>28.229166666666668</v>
@@ -7447,10 +7447,10 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B100" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C100" t="s">
         <v>19</v>
@@ -7462,7 +7462,7 @@
         <v>33</v>
       </c>
       <c r="F100" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         <v>25</v>
       </c>
       <c r="O100" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P100">
         <v>28.645833333333332</v>
@@ -7500,10 +7500,10 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B101" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C101" t="s">
         <v>19</v>
@@ -7515,7 +7515,7 @@
         <v>21</v>
       </c>
       <c r="F101" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -7542,7 +7542,7 @@
         <v>25</v>
       </c>
       <c r="O101" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P101">
         <v>25.520833333333332</v>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B102" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C102" t="s">
         <v>19</v>
@@ -7568,7 +7568,7 @@
         <v>33</v>
       </c>
       <c r="F102" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         <v>25</v>
       </c>
       <c r="O102" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P102">
         <v>25.416666666666664</v>
@@ -7606,10 +7606,10 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C103" t="s">
         <v>19</v>
@@ -7621,7 +7621,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -7648,7 +7648,7 @@
         <v>25</v>
       </c>
       <c r="O103" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P103">
         <v>23.020833333333332</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B104" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C104" t="s">
         <v>19</v>
@@ -7674,7 +7674,7 @@
         <v>21</v>
       </c>
       <c r="F104" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G104">
         <v>2</v>
@@ -7701,7 +7701,7 @@
         <v>25</v>
       </c>
       <c r="O104" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P104">
         <v>21.25</v>
@@ -7712,10 +7712,10 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C105" t="s">
         <v>19</v>
@@ -7727,7 +7727,7 @@
         <v>21</v>
       </c>
       <c r="F105" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -7754,7 +7754,7 @@
         <v>25</v>
       </c>
       <c r="O105" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P105">
         <v>19.6875</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B106" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C106" t="s">
         <v>19</v>
@@ -7780,7 +7780,7 @@
         <v>33</v>
       </c>
       <c r="F106" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -7807,7 +7807,7 @@
         <v>25</v>
       </c>
       <c r="O106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P106">
         <v>19.166666666666668</v>
@@ -7818,10 +7818,10 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B107" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s">
         <v>19</v>
@@ -7833,7 +7833,7 @@
         <v>21</v>
       </c>
       <c r="F107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G107">
         <v>3</v>
@@ -7860,7 +7860,7 @@
         <v>25</v>
       </c>
       <c r="O107" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P107">
         <v>16.145833333333336</v>
@@ -7871,10 +7871,10 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B108" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" t="s">
         <v>19</v>
@@ -7886,7 +7886,7 @@
         <v>33</v>
       </c>
       <c r="F108" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -7913,7 +7913,7 @@
         <v>25</v>
       </c>
       <c r="O108" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P108">
         <v>15</v>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C109" t="s">
         <v>19</v>
@@ -7939,7 +7939,7 @@
         <v>21</v>
       </c>
       <c r="F109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -7966,7 +7966,7 @@
         <v>25</v>
       </c>
       <c r="O109" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P109">
         <v>13.750000000000002</v>
@@ -7977,10 +7977,10 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C110" t="s">
         <v>19</v>
@@ -7992,7 +7992,7 @@
         <v>33</v>
       </c>
       <c r="F110" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>25</v>
       </c>
       <c r="O110" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P110">
         <v>13.229166666666666</v>
@@ -8030,10 +8030,10 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B111" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C111" t="s">
         <v>19</v>
@@ -8045,7 +8045,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G111">
         <v>2</v>
@@ -8072,7 +8072,7 @@
         <v>25</v>
       </c>
       <c r="O111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P111">
         <v>9.625</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B112" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C112" t="s">
         <v>19</v>
@@ -8098,7 +8098,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G112">
         <v>3</v>
@@ -8125,7 +8125,7 @@
         <v>25</v>
       </c>
       <c r="O112" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P112">
         <v>15.5</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B113" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C113" t="s">
         <v>19</v>
@@ -8151,7 +8151,7 @@
         <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -8178,7 +8178,7 @@
         <v>25</v>
       </c>
       <c r="O113" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P113">
         <v>19.9375</v>
@@ -8189,10 +8189,10 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B114" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C114" t="s">
         <v>19</v>
@@ -8204,7 +8204,7 @@
         <v>21</v>
       </c>
       <c r="F114" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -8231,7 +8231,7 @@
         <v>25</v>
       </c>
       <c r="O114" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P114">
         <v>42.5625</v>
@@ -8242,10 +8242,10 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B115" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C115" t="s">
         <v>19</v>
@@ -8257,7 +8257,7 @@
         <v>21</v>
       </c>
       <c r="F115" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8284,7 +8284,7 @@
         <v>25</v>
       </c>
       <c r="O115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P115">
         <v>44.4375</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B116" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s">
         <v>19</v>
@@ -8310,7 +8310,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -8337,7 +8337,7 @@
         <v>25</v>
       </c>
       <c r="O116" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P116">
         <v>41.875</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C117" t="s">
         <v>19</v>
@@ -8363,7 +8363,7 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G117">
         <v>2</v>
@@ -8390,7 +8390,7 @@
         <v>25</v>
       </c>
       <c r="O117" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P117">
         <v>39.625</v>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C118" t="s">
         <v>19</v>
@@ -8416,7 +8416,7 @@
         <v>21</v>
       </c>
       <c r="F118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -8443,7 +8443,7 @@
         <v>25</v>
       </c>
       <c r="O118" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P118">
         <v>37.5</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B119" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s">
         <v>19</v>
@@ -8469,7 +8469,7 @@
         <v>21</v>
       </c>
       <c r="F119" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8496,7 +8496,7 @@
         <v>25</v>
       </c>
       <c r="O119" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P119">
         <v>37.5</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C120" t="s">
         <v>19</v>
@@ -8522,7 +8522,7 @@
         <v>21</v>
       </c>
       <c r="F120" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -8549,7 +8549,7 @@
         <v>25</v>
       </c>
       <c r="O120" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P120">
         <v>35.25</v>
@@ -8560,10 +8560,10 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C121" t="s">
         <v>19</v>
@@ -8575,7 +8575,7 @@
         <v>21</v>
       </c>
       <c r="F121" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -8602,7 +8602,7 @@
         <v>25</v>
       </c>
       <c r="O121" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P121">
         <v>35.25</v>
@@ -8613,10 +8613,10 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B122" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C122" t="s">
         <v>19</v>
@@ -8628,7 +8628,7 @@
         <v>21</v>
       </c>
       <c r="F122" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         <v>25</v>
       </c>
       <c r="O122" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P122">
         <v>27.8125</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C123" t="s">
         <v>19</v>
@@ -8681,7 +8681,7 @@
         <v>21</v>
       </c>
       <c r="F123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -8702,27 +8702,27 @@
         <v>25</v>
       </c>
       <c r="M123" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N123" t="s">
         <v>25</v>
       </c>
       <c r="O123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P123">
-        <v>28.812500000000004</v>
+        <v>66.875</v>
       </c>
       <c r="Q123">
-        <v>67.6114644714257</v>
+        <v>70.49825722691006</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C124" t="s">
         <v>19</v>
@@ -8734,7 +8734,7 @@
         <v>21</v>
       </c>
       <c r="F124" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>25</v>
       </c>
       <c r="O124" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P124">
         <v>21.1875</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C125" t="s">
         <v>19</v>
@@ -8787,7 +8787,7 @@
         <v>33</v>
       </c>
       <c r="F125" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -8814,7 +8814,7 @@
         <v>25</v>
       </c>
       <c r="O125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P125">
         <v>19.21875</v>
@@ -8825,10 +8825,10 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B126" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C126" t="s">
         <v>19</v>
@@ -8840,7 +8840,7 @@
         <v>33</v>
       </c>
       <c r="F126" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -8867,7 +8867,7 @@
         <v>25</v>
       </c>
       <c r="O126" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P126">
         <v>19.21875</v>
@@ -8878,10 +8878,10 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B127" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C127" t="s">
         <v>19</v>
@@ -8893,7 +8893,7 @@
         <v>33</v>
       </c>
       <c r="F127" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -8920,7 +8920,7 @@
         <v>25</v>
       </c>
       <c r="O127" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P127">
         <v>19.84375</v>
@@ -8931,10 +8931,10 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C128" t="s">
         <v>19</v>
@@ -8946,7 +8946,7 @@
         <v>21</v>
       </c>
       <c r="F128" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -8973,7 +8973,7 @@
         <v>25</v>
       </c>
       <c r="O128" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P128">
         <v>19.21875</v>
@@ -8984,10 +8984,10 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C129" t="s">
         <v>19</v>
@@ -8999,7 +8999,7 @@
         <v>33</v>
       </c>
       <c r="F129" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9026,7 +9026,7 @@
         <v>25</v>
       </c>
       <c r="O129" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P129">
         <v>19.21875</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C130" t="s">
         <v>19</v>
@@ -9052,7 +9052,7 @@
         <v>33</v>
       </c>
       <c r="F130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>25</v>
       </c>
       <c r="O130" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P130">
         <v>19.21875</v>
@@ -9090,10 +9090,10 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C131" t="s">
         <v>19</v>
@@ -9105,7 +9105,7 @@
         <v>33</v>
       </c>
       <c r="F131" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -9132,7 +9132,7 @@
         <v>25</v>
       </c>
       <c r="O131" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P131">
         <v>18.75</v>
@@ -9143,10 +9143,10 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B132" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C132" t="s">
         <v>19</v>
@@ -9158,7 +9158,7 @@
         <v>21</v>
       </c>
       <c r="F132" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G132">
         <v>2</v>
@@ -9185,7 +9185,7 @@
         <v>25</v>
       </c>
       <c r="O132" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P132">
         <v>18.75</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C133" t="s">
         <v>19</v>
@@ -9211,7 +9211,7 @@
         <v>21</v>
       </c>
       <c r="F133" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -9238,7 +9238,7 @@
         <v>25</v>
       </c>
       <c r="O133" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P133">
         <v>49.461522979497786</v>
@@ -9249,10 +9249,10 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s">
         <v>19</v>
@@ -9264,7 +9264,7 @@
         <v>21</v>
       </c>
       <c r="F134" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -9291,7 +9291,7 @@
         <v>25</v>
       </c>
       <c r="O134" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P134">
         <v>47.793987804927696</v>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C135" t="s">
         <v>19</v>
@@ -9317,7 +9317,7 @@
         <v>21</v>
       </c>
       <c r="F135" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -9344,7 +9344,7 @@
         <v>25</v>
       </c>
       <c r="O135" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P135">
         <v>54.35990755479742</v>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C136" t="s">
         <v>19</v>
@@ -9370,7 +9370,7 @@
         <v>21</v>
       </c>
       <c r="F136" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -9391,27 +9391,27 @@
         <v>25</v>
       </c>
       <c r="M136" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N136" t="s">
         <v>25</v>
       </c>
       <c r="O136" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P136">
-        <v>45.60534788830445</v>
+        <v>54.84375</v>
       </c>
       <c r="Q136">
-        <v>15.857653599645467</v>
+        <v>24.684139110458737</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B137" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C137" t="s">
         <v>19</v>
@@ -9423,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="F137" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G137">
         <v>2</v>
@@ -9450,7 +9450,7 @@
         <v>25</v>
       </c>
       <c r="O137" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P137">
         <v>57.395833333333336</v>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B138" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C138" t="s">
         <v>19</v>
@@ -9476,7 +9476,7 @@
         <v>21</v>
       </c>
       <c r="F138" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -9503,7 +9503,7 @@
         <v>25</v>
       </c>
       <c r="O138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P138">
         <v>57.395833333333336</v>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B139" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C139" t="s">
         <v>19</v>
@@ -9529,7 +9529,7 @@
         <v>21</v>
       </c>
       <c r="F139" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -9550,27 +9550,27 @@
         <v>25</v>
       </c>
       <c r="M139" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N139" t="s">
         <v>25</v>
       </c>
       <c r="O139" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P139">
-        <v>42.79138228121743</v>
+        <v>61.09375</v>
       </c>
       <c r="Q139">
-        <v>17.65823875685186</v>
+        <v>23.78435278499767</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B140" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C140" t="s">
         <v>19</v>
@@ -9582,7 +9582,7 @@
         <v>21</v>
       </c>
       <c r="F140" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -9603,27 +9603,27 @@
         <v>25</v>
       </c>
       <c r="M140" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N140" t="s">
         <v>25</v>
       </c>
       <c r="O140" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P140">
-        <v>43.93781271373437</v>
+        <v>69.84375</v>
       </c>
       <c r="Q140">
-        <v>15.107409784142803</v>
+        <v>25.358978854554543</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B141" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C141" t="s">
         <v>19</v>
@@ -9635,7 +9635,7 @@
         <v>33</v>
       </c>
       <c r="F141" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -9650,7 +9650,7 @@
         <v>131</v>
       </c>
       <c r="K141" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L141" t="s">
         <v>25</v>
@@ -9662,7 +9662,7 @@
         <v>25</v>
       </c>
       <c r="O141" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P141">
         <v>60</v>
@@ -9673,10 +9673,10 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B142" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C142" t="s">
         <v>19</v>
@@ -9688,7 +9688,7 @@
         <v>21</v>
       </c>
       <c r="F142" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -9700,10 +9700,10 @@
         <v>24</v>
       </c>
       <c r="J142" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K142" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L142" t="s">
         <v>25</v>
@@ -9715,7 +9715,7 @@
         <v>25</v>
       </c>
       <c r="O142" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P142">
         <v>60</v>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B143" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C143" t="s">
         <v>19</v>
@@ -9741,7 +9741,7 @@
         <v>21</v>
       </c>
       <c r="F143" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -9753,10 +9753,10 @@
         <v>24</v>
       </c>
       <c r="J143" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K143" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L143" t="s">
         <v>25</v>
@@ -9768,7 +9768,7 @@
         <v>25</v>
       </c>
       <c r="O143" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P143">
         <v>60</v>
@@ -9779,10 +9779,10 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B144" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C144" t="s">
         <v>19</v>
@@ -9794,7 +9794,7 @@
         <v>33</v>
       </c>
       <c r="F144" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -9806,10 +9806,10 @@
         <v>30</v>
       </c>
       <c r="J144" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K144" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L144" t="s">
         <v>25</v>
@@ -9821,7 +9821,7 @@
         <v>25</v>
       </c>
       <c r="O144" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P144">
         <v>58.828125</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B145" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C145" t="s">
         <v>19</v>
@@ -9847,7 +9847,7 @@
         <v>33</v>
       </c>
       <c r="F145" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -9859,7 +9859,7 @@
         <v>30</v>
       </c>
       <c r="J145" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K145" t="s">
         <v>25</v>
@@ -9874,7 +9874,7 @@
         <v>25</v>
       </c>
       <c r="O145" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P145">
         <v>56.32812499999999</v>
@@ -9885,7 +9885,7 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B146" t="s">
         <v>168</v>
@@ -9900,7 +9900,7 @@
         <v>33</v>
       </c>
       <c r="F146" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -9912,7 +9912,7 @@
         <v>30</v>
       </c>
       <c r="J146" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K146" t="s">
         <v>25</v>
@@ -9927,7 +9927,7 @@
         <v>25</v>
       </c>
       <c r="O146" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P146">
         <v>53.515625</v>
@@ -9938,10 +9938,10 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B147" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C147" t="s">
         <v>19</v>
@@ -9953,7 +9953,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -9965,7 +9965,7 @@
         <v>30</v>
       </c>
       <c r="J147" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K147" t="s">
         <v>25</v>
@@ -9974,27 +9974,27 @@
         <v>25</v>
       </c>
       <c r="M147" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N147" t="s">
         <v>25</v>
       </c>
       <c r="O147" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P147">
-        <v>44.45891745578752</v>
+        <v>49.895833333333336</v>
       </c>
       <c r="Q147">
-        <v>18.858628861656122</v>
+        <v>48.21915293593007</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B148" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C148" t="s">
         <v>19</v>
@@ -10006,7 +10006,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10018,7 +10018,7 @@
         <v>24</v>
       </c>
       <c r="J148" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K148" t="s">
         <v>25</v>
@@ -10033,7 +10033,7 @@
         <v>25</v>
       </c>
       <c r="O148" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P148">
         <v>27.421875</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B149" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C149" t="s">
         <v>19</v>
@@ -10059,7 +10059,7 @@
         <v>33</v>
       </c>
       <c r="F149" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10071,7 +10071,7 @@
         <v>24</v>
       </c>
       <c r="J149" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K149" t="s">
         <v>25</v>
@@ -10086,7 +10086,7 @@
         <v>25</v>
       </c>
       <c r="O149" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P149">
         <v>27.421875</v>
@@ -10097,10 +10097,10 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B150" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C150" t="s">
         <v>19</v>
@@ -10112,7 +10112,7 @@
         <v>21</v>
       </c>
       <c r="F150" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         <v>24</v>
       </c>
       <c r="J150" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K150" t="s">
         <v>25</v>
@@ -10139,7 +10139,7 @@
         <v>25</v>
       </c>
       <c r="O150" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P150">
         <v>27.421875</v>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B151" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C151" t="s">
         <v>19</v>
@@ -10165,7 +10165,7 @@
         <v>33</v>
       </c>
       <c r="F151" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -10177,7 +10177,7 @@
         <v>24</v>
       </c>
       <c r="J151" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K151" t="s">
         <v>25</v>
@@ -10192,7 +10192,7 @@
         <v>25</v>
       </c>
       <c r="O151" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P151">
         <v>27.421875</v>
@@ -10203,10 +10203,10 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B152" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C152" t="s">
         <v>19</v>
@@ -10218,7 +10218,7 @@
         <v>21</v>
       </c>
       <c r="F152" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -10230,7 +10230,7 @@
         <v>30</v>
       </c>
       <c r="J152" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K152" t="s">
         <v>25</v>
@@ -10245,7 +10245,7 @@
         <v>25</v>
       </c>
       <c r="O152" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P152">
         <v>56.32812499999999</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C153" t="s">
         <v>61</v>
@@ -10271,7 +10271,7 @@
         <v>21</v>
       </c>
       <c r="F153" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -10283,7 +10283,7 @@
         <v>144</v>
       </c>
       <c r="J153" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K153" t="s">
         <v>25</v>
@@ -10298,7 +10298,7 @@
         <v>25</v>
       </c>
       <c r="O153" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P153">
         <v>9.753341635047551</v>
@@ -10309,7 +10309,7 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B154" t="s">
         <v>168</v>
@@ -10324,7 +10324,7 @@
         <v>21</v>
       </c>
       <c r="F154" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>30</v>
       </c>
       <c r="J154" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K154" t="s">
         <v>25</v>
@@ -10351,7 +10351,7 @@
         <v>25</v>
       </c>
       <c r="O154" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P154">
         <v>6.6267131827286345</v>
@@ -10362,10 +10362,10 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C155" t="s">
         <v>61</v>
@@ -10377,7 +10377,7 @@
         <v>21</v>
       </c>
       <c r="F155" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -10389,7 +10389,7 @@
         <v>30</v>
       </c>
       <c r="J155" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K155" t="s">
         <v>25</v>
@@ -10404,7 +10404,7 @@
         <v>25</v>
       </c>
       <c r="O155" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P155">
         <v>7.043596976371156</v>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B156" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C156" t="s">
         <v>61</v>
@@ -10430,7 +10430,7 @@
         <v>21</v>
       </c>
       <c r="F156" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -10442,7 +10442,7 @@
         <v>30</v>
       </c>
       <c r="J156" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K156" t="s">
         <v>25</v>
@@ -10457,7 +10457,7 @@
         <v>25</v>
       </c>
       <c r="O156" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P156">
         <v>6.835155079549896</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B157" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C157" t="s">
         <v>61</v>
@@ -10483,7 +10483,7 @@
         <v>21</v>
       </c>
       <c r="F157" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -10495,7 +10495,7 @@
         <v>30</v>
       </c>
       <c r="J157" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K157" t="s">
         <v>25</v>
@@ -10510,7 +10510,7 @@
         <v>25</v>
       </c>
       <c r="O157" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P157">
         <v>10.482888273921965</v>
@@ -10521,10 +10521,10 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B158" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C158" t="s">
         <v>61</v>
@@ -10536,7 +10536,7 @@
         <v>33</v>
       </c>
       <c r="F158" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -10548,10 +10548,10 @@
         <v>30</v>
       </c>
       <c r="J158" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K158" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L158" t="s">
         <v>25</v>
@@ -10563,7 +10563,7 @@
         <v>25</v>
       </c>
       <c r="O158" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P158">
         <v>6.209829389086113</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B159" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C159" t="s">
         <v>61</v>
@@ -10589,7 +10589,7 @@
         <v>21</v>
       </c>
       <c r="F159" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -10601,7 +10601,7 @@
         <v>30</v>
       </c>
       <c r="J159" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K159" t="s">
         <v>25</v>
@@ -10616,7 +10616,7 @@
         <v>25</v>
       </c>
       <c r="O159" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P159">
         <v>4.2296313692841325</v>
@@ -10627,10 +10627,10 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B160" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C160" t="s">
         <v>61</v>
@@ -10642,7 +10642,7 @@
         <v>21</v>
       </c>
       <c r="F160" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -10654,7 +10654,7 @@
         <v>30</v>
       </c>
       <c r="J160" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K160" t="s">
         <v>25</v>
@@ -10669,7 +10669,7 @@
         <v>25</v>
       </c>
       <c r="O160" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P160">
         <v>10.170225428690074</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B161" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C161" t="s">
         <v>61</v>
@@ -10695,7 +10695,7 @@
         <v>21</v>
       </c>
       <c r="F161" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -10707,7 +10707,7 @@
         <v>30</v>
       </c>
       <c r="J161" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K161" t="s">
         <v>25</v>
@@ -10722,7 +10722,7 @@
         <v>25</v>
       </c>
       <c r="O161" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P161">
         <v>10.066004480279442</v>
@@ -10733,10 +10733,10 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B162" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C162" t="s">
         <v>61</v>
@@ -10748,7 +10748,7 @@
         <v>21</v>
       </c>
       <c r="F162" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -10760,7 +10760,7 @@
         <v>30</v>
       </c>
       <c r="J162" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K162" t="s">
         <v>25</v>
@@ -10775,7 +10775,7 @@
         <v>25</v>
       </c>
       <c r="O162" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P162">
         <v>7.66892266683494</v>
@@ -10786,10 +10786,10 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B163" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C163" t="s">
         <v>61</v>
@@ -10801,7 +10801,7 @@
         <v>21</v>
       </c>
       <c r="F163" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -10813,7 +10813,7 @@
         <v>30</v>
       </c>
       <c r="J163" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K163" t="s">
         <v>25</v>
@@ -10828,7 +10828,7 @@
         <v>25</v>
       </c>
       <c r="O163" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P163">
         <v>9.0625</v>
@@ -10839,10 +10839,10 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B164" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C164" t="s">
         <v>61</v>
@@ -10854,7 +10854,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -10866,7 +10866,7 @@
         <v>30</v>
       </c>
       <c r="J164" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K164" t="s">
         <v>25</v>
@@ -10881,7 +10881,7 @@
         <v>25</v>
       </c>
       <c r="O164" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P164">
         <v>9.0625</v>
@@ -10892,10 +10892,10 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B165" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C165" t="s">
         <v>61</v>
@@ -10907,7 +10907,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -10919,7 +10919,7 @@
         <v>24</v>
       </c>
       <c r="J165" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K165" t="s">
         <v>25</v>
@@ -10934,7 +10934,7 @@
         <v>25</v>
       </c>
       <c r="O165" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P165">
         <v>7.147817924781788</v>
@@ -10945,10 +10945,10 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B166" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C166" t="s">
         <v>61</v>
@@ -10960,7 +10960,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -10972,10 +10972,10 @@
         <v>24</v>
       </c>
       <c r="J166" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K166" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L166" t="s">
         <v>25</v>
@@ -10987,7 +10987,7 @@
         <v>25</v>
       </c>
       <c r="O166" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P166">
         <v>8.919574047762506</v>
@@ -11001,7 +11001,7 @@
         <v>59</v>
       </c>
       <c r="B167" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C167" t="s">
         <v>19</v>
@@ -11013,7 +11013,7 @@
         <v>33</v>
       </c>
       <c r="F167" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -11025,7 +11025,7 @@
         <v>30</v>
       </c>
       <c r="J167" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K167" t="s">
         <v>25</v>
@@ -11040,7 +11040,7 @@
         <v>25</v>
       </c>
       <c r="O167" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P167">
         <v>82.65625</v>
@@ -11054,7 +11054,7 @@
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C168" t="s">
         <v>19</v>
@@ -11066,7 +11066,7 @@
         <v>21</v>
       </c>
       <c r="F168" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -11078,7 +11078,7 @@
         <v>30</v>
       </c>
       <c r="J168" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K168" t="s">
         <v>25</v>
@@ -11093,7 +11093,7 @@
         <v>25</v>
       </c>
       <c r="O168" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P168">
         <v>83.125</v>
@@ -11107,7 +11107,7 @@
         <v>59</v>
       </c>
       <c r="B169" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C169" t="s">
         <v>19</v>
@@ -11119,7 +11119,7 @@
         <v>21</v>
       </c>
       <c r="F169" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -11131,7 +11131,7 @@
         <v>24</v>
       </c>
       <c r="J169" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K169" t="s">
         <v>25</v>
@@ -11140,19 +11140,19 @@
         <v>25</v>
       </c>
       <c r="M169" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="N169" t="s">
         <v>25</v>
       </c>
       <c r="O169" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P169">
-        <v>78.43494822793853</v>
+        <v>76.40625</v>
       </c>
       <c r="Q169">
-        <v>30.962563181619906</v>
+        <v>31.432536551416785</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -11160,7 +11160,7 @@
         <v>59</v>
       </c>
       <c r="B170" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C170" t="s">
         <v>19</v>
@@ -11172,7 +11172,7 @@
         <v>21</v>
       </c>
       <c r="F170" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G170">
         <v>2</v>
@@ -11184,7 +11184,7 @@
         <v>30</v>
       </c>
       <c r="J170" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K170" t="s">
         <v>25</v>
@@ -11199,7 +11199,7 @@
         <v>25</v>
       </c>
       <c r="O170" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P170">
         <v>81.40625</v>
@@ -11213,7 +11213,7 @@
         <v>59</v>
       </c>
       <c r="B171" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C171" t="s">
         <v>19</v>
@@ -11225,7 +11225,7 @@
         <v>21</v>
       </c>
       <c r="F171" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -11237,7 +11237,7 @@
         <v>24</v>
       </c>
       <c r="J171" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K171" t="s">
         <v>25</v>
@@ -11252,7 +11252,7 @@
         <v>25</v>
       </c>
       <c r="O171" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P171">
         <v>82.734375</v>
@@ -11266,7 +11266,7 @@
         <v>59</v>
       </c>
       <c r="B172" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C172" t="s">
         <v>19</v>
@@ -11278,7 +11278,7 @@
         <v>21</v>
       </c>
       <c r="F172" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -11290,7 +11290,7 @@
         <v>24</v>
       </c>
       <c r="J172" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K172" t="s">
         <v>25</v>
@@ -11305,7 +11305,7 @@
         <v>25</v>
       </c>
       <c r="O172" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P172">
         <v>82.8125</v>
@@ -11319,7 +11319,7 @@
         <v>59</v>
       </c>
       <c r="B173" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C173" t="s">
         <v>19</v>
@@ -11331,7 +11331,7 @@
         <v>33</v>
       </c>
       <c r="F173" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G173">
         <v>0</v>
@@ -11343,7 +11343,7 @@
         <v>24</v>
       </c>
       <c r="J173" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K173" t="s">
         <v>25</v>
@@ -11358,7 +11358,7 @@
         <v>25</v>
       </c>
       <c r="O173" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P173">
         <v>81.66579603838262</v>
@@ -11372,7 +11372,7 @@
         <v>59</v>
       </c>
       <c r="B174" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C174" t="s">
         <v>19</v>
@@ -11384,7 +11384,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -11396,7 +11396,7 @@
         <v>30</v>
       </c>
       <c r="J174" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K174" t="s">
         <v>25</v>
@@ -11411,7 +11411,7 @@
         <v>25</v>
       </c>
       <c r="O174" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P174">
         <v>82.734375</v>
@@ -11425,7 +11425,7 @@
         <v>59</v>
       </c>
       <c r="B175" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C175" t="s">
         <v>19</v>
@@ -11437,7 +11437,7 @@
         <v>33</v>
       </c>
       <c r="F175" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -11449,7 +11449,7 @@
         <v>30</v>
       </c>
       <c r="J175" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K175" t="s">
         <v>25</v>
@@ -11464,7 +11464,7 @@
         <v>25</v>
       </c>
       <c r="O175" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P175">
         <v>93.23432290224808</v>
@@ -11478,7 +11478,7 @@
         <v>59</v>
       </c>
       <c r="B176" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C176" t="s">
         <v>19</v>
@@ -11490,7 +11490,7 @@
         <v>21</v>
       </c>
       <c r="F176" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -11502,7 +11502,7 @@
         <v>24</v>
       </c>
       <c r="J176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K176" t="s">
         <v>25</v>
@@ -11517,7 +11517,7 @@
         <v>25</v>
       </c>
       <c r="O176" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P176">
         <v>69.57616602274948</v>
@@ -11531,7 +11531,7 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C177" t="s">
         <v>19</v>
@@ -11543,7 +11543,7 @@
         <v>21</v>
       </c>
       <c r="F177" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G177">
         <v>2</v>
@@ -11555,7 +11555,7 @@
         <v>30</v>
       </c>
       <c r="J177" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K177" t="s">
         <v>25</v>
@@ -11570,7 +11570,7 @@
         <v>25</v>
       </c>
       <c r="O177" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P177">
         <v>68.42973559023254</v>
@@ -11584,7 +11584,7 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C178" t="s">
         <v>19</v>
@@ -11596,7 +11596,7 @@
         <v>21</v>
       </c>
       <c r="F178" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -11608,7 +11608,7 @@
         <v>30</v>
       </c>
       <c r="J178" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K178" t="s">
         <v>25</v>
@@ -11623,7 +11623,7 @@
         <v>25</v>
       </c>
       <c r="O178" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P178">
         <v>71.55636404255145</v>
@@ -11637,7 +11637,7 @@
         <v>59</v>
       </c>
       <c r="B179" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C179" t="s">
         <v>19</v>
@@ -11649,7 +11649,7 @@
         <v>21</v>
       </c>
       <c r="F179" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>30</v>
       </c>
       <c r="J179" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K179" t="s">
         <v>25</v>
@@ -11676,7 +11676,7 @@
         <v>25</v>
       </c>
       <c r="O179" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P179">
         <v>69.36772412592822</v>
@@ -11690,7 +11690,7 @@
         <v>59</v>
       </c>
       <c r="B180" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C180" t="s">
         <v>19</v>
@@ -11702,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="F180" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -11714,7 +11714,7 @@
         <v>30</v>
       </c>
       <c r="J180" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K180" t="s">
         <v>25</v>
@@ -11729,7 +11729,7 @@
         <v>25</v>
       </c>
       <c r="O180" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P180">
         <v>70.93103835208767</v>
@@ -11743,7 +11743,7 @@
         <v>59</v>
       </c>
       <c r="B181" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C181" t="s">
         <v>19</v>
@@ -11755,7 +11755,7 @@
         <v>21</v>
       </c>
       <c r="F181" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -11767,7 +11767,7 @@
         <v>30</v>
       </c>
       <c r="J181" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K181" t="s">
         <v>25</v>
@@ -11782,7 +11782,7 @@
         <v>25</v>
       </c>
       <c r="O181" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P181">
         <v>71.55636404255145</v>
@@ -11796,7 +11796,7 @@
         <v>59</v>
       </c>
       <c r="B182" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C182" t="s">
         <v>19</v>
@@ -11808,7 +11808,7 @@
         <v>21</v>
       </c>
       <c r="F182" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -11820,7 +11820,7 @@
         <v>24</v>
       </c>
       <c r="J182" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K182" t="s">
         <v>25</v>
@@ -11835,7 +11835,7 @@
         <v>25</v>
       </c>
       <c r="O182" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P182">
         <v>70.40993361003453</v>
@@ -11849,7 +11849,7 @@
         <v>59</v>
       </c>
       <c r="B183" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C183" t="s">
         <v>19</v>
@@ -11861,7 +11861,7 @@
         <v>21</v>
       </c>
       <c r="F183" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -11873,7 +11873,7 @@
         <v>24</v>
       </c>
       <c r="J183" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K183" t="s">
         <v>25</v>
@@ -11888,7 +11888,7 @@
         <v>25</v>
       </c>
       <c r="O183" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P183">
         <v>70.61837550685578</v>
@@ -11899,10 +11899,10 @@
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B184" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C184" t="s">
         <v>19</v>
@@ -11914,7 +11914,7 @@
         <v>21</v>
       </c>
       <c r="F184" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -11926,7 +11926,7 @@
         <v>24</v>
       </c>
       <c r="J184" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K184" t="s">
         <v>25</v>
@@ -11941,7 +11941,7 @@
         <v>25</v>
       </c>
       <c r="O184" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P184">
         <v>58.111861697580125</v>
@@ -11952,10 +11952,10 @@
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B185" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C185" t="s">
         <v>19</v>
@@ -11967,7 +11967,7 @@
         <v>21</v>
       </c>
       <c r="F185" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -11979,7 +11979,7 @@
         <v>30</v>
       </c>
       <c r="J185" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K185" t="s">
         <v>25</v>
@@ -11994,7 +11994,7 @@
         <v>25</v>
       </c>
       <c r="O185" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P185">
         <v>61.75959489195218</v>
@@ -12005,10 +12005,10 @@
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B186" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C186" t="s">
         <v>19</v>
@@ -12020,7 +12020,7 @@
         <v>21</v>
       </c>
       <c r="F186" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -12032,7 +12032,7 @@
         <v>30</v>
       </c>
       <c r="J186" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K186" t="s">
         <v>25</v>
@@ -12047,7 +12047,7 @@
         <v>25</v>
       </c>
       <c r="O186" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P186">
         <v>60.82160635625652</v>
@@ -12058,10 +12058,10 @@
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B187" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C187" t="s">
         <v>19</v>
@@ -12073,7 +12073,7 @@
         <v>21</v>
       </c>
       <c r="F187" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -12085,7 +12085,7 @@
         <v>30</v>
       </c>
       <c r="J187" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K187" t="s">
         <v>25</v>
@@ -12100,7 +12100,7 @@
         <v>25</v>
       </c>
       <c r="O187" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P187">
         <v>62.072257737184074</v>
@@ -12111,10 +12111,10 @@
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B188" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C188" t="s">
         <v>19</v>
@@ -12126,7 +12126,7 @@
         <v>21</v>
       </c>
       <c r="F188" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -12138,7 +12138,7 @@
         <v>24</v>
       </c>
       <c r="J188" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K188" t="s">
         <v>25</v>
@@ -12153,7 +12153,7 @@
         <v>25</v>
       </c>
       <c r="O188" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P188">
         <v>61.551152995130934</v>
@@ -12164,10 +12164,10 @@
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B189" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C189" t="s">
         <v>19</v>
@@ -12179,7 +12179,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -12191,7 +12191,7 @@
         <v>30</v>
       </c>
       <c r="J189" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K189" t="s">
         <v>25</v>
@@ -12206,7 +12206,7 @@
         <v>25</v>
       </c>
       <c r="O189" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P189">
         <v>59.7793968721502</v>
@@ -12217,10 +12217,10 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B190" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C190" t="s">
         <v>19</v>
@@ -12232,7 +12232,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -12244,7 +12244,7 @@
         <v>24</v>
       </c>
       <c r="J190" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K190" t="s">
         <v>25</v>
@@ -12259,7 +12259,7 @@
         <v>25</v>
       </c>
       <c r="O190" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P190">
         <v>61.96803678877345</v>
@@ -12270,10 +12270,10 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B191" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C191" t="s">
         <v>19</v>
@@ -12285,7 +12285,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -12297,7 +12297,7 @@
         <v>30</v>
       </c>
       <c r="J191" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K191" t="s">
         <v>25</v>
@@ -12312,7 +12312,7 @@
         <v>25</v>
       </c>
       <c r="O191" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P191">
         <v>50.08684866996157</v>
@@ -12323,13 +12323,13 @@
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B192" t="s">
         <v>25</v>
       </c>
       <c r="C192" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D192" t="s">
         <v>25</v>
@@ -12338,7 +12338,7 @@
         <v>21</v>
       </c>
       <c r="F192" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -12359,7 +12359,7 @@
         <v>25</v>
       </c>
       <c r="M192" t="s">
-        <v>590</v>
+        <v>226</v>
       </c>
       <c r="N192" t="s">
         <v>25</v>
@@ -12368,10 +12368,10 @@
         <v>591</v>
       </c>
       <c r="P192">
-        <v>47.15625</v>
+        <v>47.5</v>
       </c>
       <c r="Q192">
-        <v>50.10666707356771</v>
+        <v>49.20331647927297</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -12412,7 +12412,7 @@
         <v>25</v>
       </c>
       <c r="M193" t="s">
-        <v>590</v>
+        <v>226</v>
       </c>
       <c r="N193" t="s">
         <v>25</v>
